--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Höchst/Datenbank.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_FT_Höchst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_HB_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71F4327-B46A-4F20-9CFE-C1BB2B498537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEE9695-3B9B-47E4-906C-62E0B154718A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1344,6 +1344,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1389,26 +1392,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1419,33 +1413,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1804,10 +1804,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="84" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1824,8 +1824,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="71"/>
-      <c r="B3" s="82"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="85"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1840,8 +1840,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="71"/>
-      <c r="B4" s="82"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="85"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1856,8 +1856,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="71"/>
-      <c r="B5" s="82"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="85"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1872,8 +1872,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="74"/>
+      <c r="B6" s="85"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1888,8 +1888,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="71"/>
-      <c r="B7" s="82"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="85"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1904,8 +1904,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
-      <c r="B8" s="83" t="s">
+      <c r="A8" s="74"/>
+      <c r="B8" s="86" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1922,8 +1922,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
-      <c r="B9" s="82"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="85"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -1938,41 +1938,41 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="82"/>
+      <c r="A10" s="74"/>
+      <c r="B10" s="85"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="103">
+      <c r="E10" s="70">
         <v>0</v>
       </c>
-      <c r="F10" s="103" t="s">
+      <c r="F10" s="70" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="71"/>
-      <c r="B11" s="82"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="85"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="104">
+      <c r="E11" s="71">
         <f>0.05*9070</f>
         <v>453.5</v>
       </c>
-      <c r="F11" s="105" t="s">
+      <c r="F11" s="72" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
-      <c r="B12" s="82"/>
+      <c r="A12" s="74"/>
+      <c r="B12" s="85"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -1987,8 +1987,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="82"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="85"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -2003,8 +2003,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
-      <c r="B14" s="82"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="85"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -2019,8 +2019,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
-      <c r="B15" s="84"/>
+      <c r="A15" s="74"/>
+      <c r="B15" s="87"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -2035,8 +2035,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="71"/>
-      <c r="B16" s="75" t="s">
+      <c r="A16" s="74"/>
+      <c r="B16" s="78" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -2054,8 +2054,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="71"/>
-      <c r="B17" s="75"/>
+      <c r="A17" s="74"/>
+      <c r="B17" s="78"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
@@ -2070,8 +2070,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="71"/>
-      <c r="B18" s="75"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="78"/>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -2086,8 +2086,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="71"/>
-      <c r="B19" s="75"/>
+      <c r="A19" s="74"/>
+      <c r="B19" s="78"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -2102,8 +2102,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="71"/>
-      <c r="B20" s="75"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="78"/>
       <c r="C20" t="s">
         <v>17</v>
       </c>
@@ -2118,10 +2118,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="77" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2138,8 +2138,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="71"/>
-      <c r="B22" s="75"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="78"/>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -2154,8 +2154,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="71"/>
-      <c r="B23" s="75"/>
+      <c r="A23" s="74"/>
+      <c r="B23" s="78"/>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -2170,8 +2170,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="71"/>
-      <c r="B24" s="75"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="78"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
@@ -2186,8 +2186,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="71"/>
-      <c r="B25" s="75"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="78"/>
       <c r="C25" t="s">
         <v>47</v>
       </c>
@@ -2202,8 +2202,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="71"/>
-      <c r="B26" s="75"/>
+      <c r="A26" s="74"/>
+      <c r="B26" s="78"/>
       <c r="C26" t="s">
         <v>48</v>
       </c>
@@ -2218,8 +2218,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="71"/>
-      <c r="B27" s="75"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="78"/>
       <c r="C27" t="s">
         <v>17</v>
       </c>
@@ -2234,8 +2234,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="71"/>
-      <c r="B28" s="75"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="78"/>
       <c r="C28" t="s">
         <v>114</v>
       </c>
@@ -2250,8 +2250,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="71"/>
-      <c r="B29" s="76" t="s">
+      <c r="A29" s="74"/>
+      <c r="B29" s="79" t="s">
         <v>258</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -2268,8 +2268,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="71"/>
-      <c r="B30" s="79"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="82"/>
       <c r="C30" s="51" t="s">
         <v>23</v>
       </c>
@@ -2285,8 +2285,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="71"/>
-      <c r="B31" s="79"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="82"/>
       <c r="C31" s="51" t="s">
         <v>18</v>
       </c>
@@ -2301,8 +2301,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="71"/>
-      <c r="B32" s="79"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="82"/>
       <c r="C32" s="51" t="s">
         <v>19</v>
       </c>
@@ -2317,8 +2317,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="71"/>
-      <c r="B33" s="79"/>
+      <c r="A33" s="74"/>
+      <c r="B33" s="82"/>
       <c r="C33" s="51" t="s">
         <v>47</v>
       </c>
@@ -2333,8 +2333,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="71"/>
-      <c r="B34" s="79"/>
+      <c r="A34" s="74"/>
+      <c r="B34" s="82"/>
       <c r="C34" s="51" t="s">
         <v>48</v>
       </c>
@@ -2349,8 +2349,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="71"/>
-      <c r="B35" s="79"/>
+      <c r="A35" s="74"/>
+      <c r="B35" s="82"/>
       <c r="C35" s="51" t="s">
         <v>115</v>
       </c>
@@ -2365,8 +2365,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="71"/>
-      <c r="B36" s="79"/>
+      <c r="A36" s="74"/>
+      <c r="B36" s="82"/>
       <c r="C36" s="51" t="s">
         <v>114</v>
       </c>
@@ -2381,8 +2381,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="71"/>
-      <c r="B37" s="79"/>
+      <c r="A37" s="74"/>
+      <c r="B37" s="82"/>
       <c r="C37" s="51" t="s">
         <v>15</v>
       </c>
@@ -2397,8 +2397,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="72"/>
-      <c r="B38" s="80"/>
+      <c r="A38" s="75"/>
+      <c r="B38" s="83"/>
       <c r="C38" s="14" t="s">
         <v>17</v>
       </c>
@@ -2413,7 +2413,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="73" t="s">
         <v>86</v>
       </c>
       <c r="B39" s="57" t="s">
@@ -2433,7 +2433,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="73"/>
+      <c r="A40" s="76"/>
       <c r="B40" s="67" t="s">
         <v>302</v>
       </c>
@@ -2444,14 +2444,14 @@
         <v>304</v>
       </c>
       <c r="E40" s="69">
-        <v>18</v>
+        <v>0.2</v>
       </c>
       <c r="F40" s="68" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="73"/>
+      <c r="A41" s="76"/>
       <c r="B41" s="60" t="s">
         <v>299</v>
       </c>
@@ -2469,8 +2469,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="71"/>
-      <c r="B42" s="76" t="s">
+      <c r="A42" s="74"/>
+      <c r="B42" s="79" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2487,8 +2487,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="71"/>
-      <c r="B43" s="75"/>
+      <c r="A43" s="74"/>
+      <c r="B43" s="78"/>
       <c r="C43" t="s">
         <v>12</v>
       </c>
@@ -2503,8 +2503,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="71"/>
-      <c r="B44" s="75"/>
+      <c r="A44" s="74"/>
+      <c r="B44" s="78"/>
       <c r="C44" t="s">
         <v>19</v>
       </c>
@@ -2519,8 +2519,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="71"/>
-      <c r="B45" s="75"/>
+      <c r="A45" s="74"/>
+      <c r="B45" s="78"/>
       <c r="C45" t="s">
         <v>20</v>
       </c>
@@ -2535,8 +2535,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="71"/>
-      <c r="B46" s="75"/>
+      <c r="A46" s="74"/>
+      <c r="B46" s="78"/>
       <c r="C46" t="s">
         <v>15</v>
       </c>
@@ -2551,8 +2551,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="71"/>
-      <c r="B47" s="75"/>
+      <c r="A47" s="74"/>
+      <c r="B47" s="78"/>
       <c r="C47" t="s">
         <v>82</v>
       </c>
@@ -2567,8 +2567,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="71"/>
-      <c r="B48" s="77"/>
+      <c r="A48" s="74"/>
+      <c r="B48" s="80"/>
       <c r="C48" s="5" t="s">
         <v>17</v>
       </c>
@@ -2583,8 +2583,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="71"/>
-      <c r="B49" s="76" t="s">
+      <c r="A49" s="74"/>
+      <c r="B49" s="79" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -2601,8 +2601,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="71"/>
-      <c r="B50" s="75"/>
+      <c r="A50" s="74"/>
+      <c r="B50" s="78"/>
       <c r="C50" t="s">
         <v>12</v>
       </c>
@@ -2617,8 +2617,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="71"/>
-      <c r="B51" s="75"/>
+      <c r="A51" s="74"/>
+      <c r="B51" s="78"/>
       <c r="C51" t="s">
         <v>19</v>
       </c>
@@ -2633,8 +2633,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="71"/>
-      <c r="B52" s="75"/>
+      <c r="A52" s="74"/>
+      <c r="B52" s="78"/>
       <c r="C52" t="s">
         <v>20</v>
       </c>
@@ -2649,8 +2649,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="71"/>
-      <c r="B53" s="75"/>
+      <c r="A53" s="74"/>
+      <c r="B53" s="78"/>
       <c r="C53" t="s">
         <v>15</v>
       </c>
@@ -2665,8 +2665,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="71"/>
-      <c r="B54" s="75"/>
+      <c r="A54" s="74"/>
+      <c r="B54" s="78"/>
       <c r="C54" t="s">
         <v>82</v>
       </c>
@@ -2681,8 +2681,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="72"/>
-      <c r="B55" s="78"/>
+      <c r="A55" s="75"/>
+      <c r="B55" s="81"/>
       <c r="C55" s="14" t="s">
         <v>17</v>
       </c>
@@ -2697,7 +2697,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="70" t="s">
+      <c r="A56" s="73" t="s">
         <v>90</v>
       </c>
       <c r="B56" s="16" t="s">
@@ -2717,7 +2717,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="71"/>
+      <c r="A57" s="74"/>
       <c r="B57" s="17" t="s">
         <v>93</v>
       </c>
@@ -2735,7 +2735,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="72"/>
+      <c r="A58" s="75"/>
       <c r="B58" s="1" t="s">
         <v>94</v>
       </c>
@@ -2810,7 +2810,7 @@
       <c r="A2" s="92" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="95" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="28" t="s">
@@ -2826,7 +2826,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="94"/>
-      <c r="B3" s="98"/>
+      <c r="B3" s="89"/>
       <c r="C3" s="12" t="s">
         <v>136</v>
       </c>
@@ -2840,7 +2840,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="94"/>
-      <c r="B4" s="98"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="94"/>
-      <c r="B5" s="98"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="12" t="s">
         <v>172</v>
       </c>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="94"/>
-      <c r="B6" s="98"/>
+      <c r="B6" s="89"/>
       <c r="C6" s="12" t="s">
         <v>184</v>
       </c>
@@ -2882,7 +2882,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="94"/>
-      <c r="B7" s="98"/>
+      <c r="B7" s="89"/>
       <c r="C7" s="12" t="s">
         <v>202</v>
       </c>
@@ -2896,7 +2896,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="94"/>
-      <c r="B8" s="98"/>
+      <c r="B8" s="89"/>
       <c r="C8" s="12" t="s">
         <v>251</v>
       </c>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="94"/>
-      <c r="B9" s="98"/>
+      <c r="B9" s="89"/>
       <c r="C9" s="12" t="s">
         <v>216</v>
       </c>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="94"/>
-      <c r="B10" s="98"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="12" t="s">
         <v>241</v>
       </c>
@@ -2938,12 +2938,12 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="94"/>
-      <c r="B11" s="98"/>
+      <c r="B11" s="89"/>
       <c r="E11" s="35"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="94"/>
-      <c r="B12" s="100" t="s">
+      <c r="B12" s="88" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="37" t="s">
@@ -2959,7 +2959,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="94"/>
-      <c r="B13" s="98"/>
+      <c r="B13" s="89"/>
       <c r="C13" s="12" t="s">
         <v>177</v>
       </c>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="94"/>
-      <c r="B14" s="98"/>
+      <c r="B14" s="89"/>
       <c r="C14" s="12" t="s">
         <v>180</v>
       </c>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="94"/>
-      <c r="B15" s="98"/>
+      <c r="B15" s="89"/>
       <c r="C15" s="12" t="s">
         <v>181</v>
       </c>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="94"/>
-      <c r="B16" s="98"/>
+      <c r="B16" s="89"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="94"/>
-      <c r="B17" s="98"/>
+      <c r="B17" s="89"/>
       <c r="C17" s="12" t="s">
         <v>184</v>
       </c>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="94"/>
-      <c r="B18" s="98"/>
+      <c r="B18" s="89"/>
       <c r="C18" s="12" t="s">
         <v>202</v>
       </c>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="94"/>
-      <c r="B19" s="98"/>
+      <c r="B19" s="89"/>
       <c r="C19" s="12" t="s">
         <v>251</v>
       </c>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="94"/>
-      <c r="B20" s="98"/>
+      <c r="B20" s="89"/>
       <c r="C20" s="12" t="s">
         <v>216</v>
       </c>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="94"/>
-      <c r="B21" s="98"/>
+      <c r="B21" s="89"/>
       <c r="C21" s="12" t="s">
         <v>241</v>
       </c>
@@ -3085,7 +3085,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="94"/>
-      <c r="B22" s="99"/>
+      <c r="B22" s="91"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
       <c r="E22" s="40"/>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="94"/>
-      <c r="B23" s="89" t="s">
+      <c r="B23" s="96" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -3109,7 +3109,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="94"/>
-      <c r="B24" s="89"/>
+      <c r="B24" s="96"/>
       <c r="C24" s="12" t="s">
         <v>136</v>
       </c>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="94"/>
-      <c r="B25" s="89"/>
+      <c r="B25" s="96"/>
       <c r="C25" s="12" t="s">
         <v>102</v>
       </c>
@@ -3137,7 +3137,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="94"/>
-      <c r="B26" s="89"/>
+      <c r="B26" s="96"/>
       <c r="C26" s="12" t="s">
         <v>174</v>
       </c>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="94"/>
-      <c r="B27" s="89"/>
+      <c r="B27" s="96"/>
       <c r="C27" s="12" t="s">
         <v>184</v>
       </c>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="94"/>
-      <c r="B28" s="89"/>
+      <c r="B28" s="96"/>
       <c r="C28" s="12" t="s">
         <v>202</v>
       </c>
@@ -3179,7 +3179,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="94"/>
-      <c r="B29" s="89"/>
+      <c r="B29" s="96"/>
       <c r="C29" s="12" t="s">
         <v>251</v>
       </c>
@@ -3193,7 +3193,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="94"/>
-      <c r="B30" s="89"/>
+      <c r="B30" s="96"/>
       <c r="C30" s="12" t="s">
         <v>216</v>
       </c>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="94"/>
-      <c r="B31" s="89"/>
+      <c r="B31" s="96"/>
       <c r="C31" s="12" t="s">
         <v>241</v>
       </c>
@@ -3221,14 +3221,14 @@
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="94"/>
-      <c r="B32" s="89"/>
+      <c r="B32" s="96"/>
       <c r="E32" s="35"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="101" t="s">
+      <c r="B33" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="28" t="s">
@@ -3244,7 +3244,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="94"/>
-      <c r="B34" s="89"/>
+      <c r="B34" s="96"/>
       <c r="C34" s="12" t="s">
         <v>140</v>
       </c>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="94"/>
-      <c r="B35" s="89"/>
+      <c r="B35" s="96"/>
       <c r="C35" s="12" t="s">
         <v>169</v>
       </c>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="94"/>
-      <c r="B36" s="89"/>
+      <c r="B36" s="96"/>
       <c r="C36" s="12" t="s">
         <v>170</v>
       </c>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="94"/>
-      <c r="B37" s="89"/>
+      <c r="B37" s="96"/>
       <c r="C37" s="12" t="s">
         <v>184</v>
       </c>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="94"/>
-      <c r="B38" s="89"/>
+      <c r="B38" s="96"/>
       <c r="C38" s="12" t="s">
         <v>202</v>
       </c>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="94"/>
-      <c r="B39" s="89"/>
+      <c r="B39" s="96"/>
       <c r="C39" s="12" t="s">
         <v>251</v>
       </c>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="94"/>
-      <c r="B40" s="89"/>
+      <c r="B40" s="96"/>
       <c r="C40" s="12" t="s">
         <v>216</v>
       </c>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="94"/>
-      <c r="B41" s="89"/>
+      <c r="B41" s="96"/>
       <c r="C41" s="12" t="s">
         <v>241</v>
       </c>
@@ -3356,12 +3356,12 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="94"/>
-      <c r="B42" s="89"/>
+      <c r="B42" s="96"/>
       <c r="E42" s="35"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="94"/>
-      <c r="B43" s="88" t="s">
+      <c r="B43" s="99" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="37" t="s">
@@ -3377,7 +3377,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="94"/>
-      <c r="B44" s="89"/>
+      <c r="B44" s="96"/>
       <c r="C44" s="12" t="s">
         <v>142</v>
       </c>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="94"/>
-      <c r="B45" s="98"/>
+      <c r="B45" s="89"/>
       <c r="C45" s="12" t="s">
         <v>140</v>
       </c>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="94"/>
-      <c r="B46" s="98"/>
+      <c r="B46" s="89"/>
       <c r="C46" s="12" t="s">
         <v>136</v>
       </c>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="94"/>
-      <c r="B47" s="98"/>
+      <c r="B47" s="89"/>
       <c r="C47" s="12" t="s">
         <v>157</v>
       </c>
@@ -3433,7 +3433,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="94"/>
-      <c r="B48" s="98"/>
+      <c r="B48" s="89"/>
       <c r="C48" s="12" t="s">
         <v>158</v>
       </c>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="94"/>
-      <c r="B49" s="98"/>
+      <c r="B49" s="89"/>
       <c r="C49" s="12" t="s">
         <v>184</v>
       </c>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="94"/>
-      <c r="B50" s="98"/>
+      <c r="B50" s="89"/>
       <c r="C50" s="12" t="s">
         <v>202</v>
       </c>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="94"/>
-      <c r="B51" s="98"/>
+      <c r="B51" s="89"/>
       <c r="C51" s="12" t="s">
         <v>251</v>
       </c>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="94"/>
-      <c r="B52" s="98"/>
+      <c r="B52" s="89"/>
       <c r="C52" s="12" t="s">
         <v>216</v>
       </c>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="94"/>
-      <c r="B53" s="98"/>
+      <c r="B53" s="89"/>
       <c r="C53" s="12" t="s">
         <v>241</v>
       </c>
@@ -3516,8 +3516,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="95"/>
-      <c r="B54" s="102"/>
+      <c r="A54" s="97"/>
+      <c r="B54" s="100"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43"/>
       <c r="E54" s="44"/>
@@ -3527,7 +3527,7 @@
       <c r="A55" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="96" t="s">
+      <c r="B55" s="95" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="28" t="s">
@@ -3543,7 +3543,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="94"/>
-      <c r="B56" s="98"/>
+      <c r="B56" s="89"/>
       <c r="C56" s="12" t="s">
         <v>200</v>
       </c>
@@ -3557,12 +3557,12 @@
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="94"/>
-      <c r="B57" s="99"/>
+      <c r="B57" s="91"/>
       <c r="E57" s="33"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="94"/>
-      <c r="B58" s="85" t="s">
+      <c r="B58" s="101" t="s">
         <v>305</v>
       </c>
       <c r="C58" s="63" t="s">
@@ -3578,7 +3578,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="94"/>
-      <c r="B59" s="86"/>
+      <c r="B59" s="102"/>
       <c r="C59" s="65" t="s">
         <v>200</v>
       </c>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="94"/>
-      <c r="B60" s="87"/>
+      <c r="B60" s="103"/>
       <c r="C60" s="65"/>
       <c r="D60" s="65"/>
       <c r="E60" s="66"/>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="94"/>
-      <c r="B61" s="88" t="s">
+      <c r="B61" s="99" t="s">
         <v>6</v>
       </c>
       <c r="C61" s="37" t="s">
@@ -3616,7 +3616,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="94"/>
-      <c r="B62" s="89"/>
+      <c r="B62" s="96"/>
       <c r="C62" s="12" t="s">
         <v>136</v>
       </c>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="94"/>
-      <c r="B63" s="89"/>
+      <c r="B63" s="96"/>
       <c r="C63" s="12" t="s">
         <v>152</v>
       </c>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="94"/>
-      <c r="B64" s="89"/>
+      <c r="B64" s="96"/>
       <c r="C64" s="12" t="s">
         <v>184</v>
       </c>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="94"/>
-      <c r="B65" s="89"/>
+      <c r="B65" s="96"/>
       <c r="C65" s="12" t="s">
         <v>202</v>
       </c>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="94"/>
-      <c r="B66" s="89"/>
+      <c r="B66" s="96"/>
       <c r="C66" s="12" t="s">
         <v>210</v>
       </c>
@@ -3686,7 +3686,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="94"/>
-      <c r="B67" s="89"/>
+      <c r="B67" s="96"/>
       <c r="C67" s="12" t="s">
         <v>251</v>
       </c>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="94"/>
-      <c r="B68" s="89"/>
+      <c r="B68" s="96"/>
       <c r="C68" s="12" t="s">
         <v>216</v>
       </c>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="94"/>
-      <c r="B69" s="89"/>
+      <c r="B69" s="96"/>
       <c r="C69" s="12" t="s">
         <v>241</v>
       </c>
@@ -3728,11 +3728,11 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="94"/>
-      <c r="B70" s="90"/>
+      <c r="B70" s="104"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="94"/>
-      <c r="B71" s="88" t="s">
+      <c r="B71" s="99" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="37" t="s">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="94"/>
-      <c r="B72" s="89"/>
+      <c r="B72" s="96"/>
       <c r="C72" s="12" t="s">
         <v>137</v>
       </c>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="94"/>
-      <c r="B73" s="89"/>
+      <c r="B73" s="96"/>
       <c r="C73" s="12" t="s">
         <v>150</v>
       </c>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="94"/>
-      <c r="B74" s="89"/>
+      <c r="B74" s="96"/>
       <c r="C74" s="12" t="s">
         <v>184</v>
       </c>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="94"/>
-      <c r="B75" s="89"/>
+      <c r="B75" s="96"/>
       <c r="C75" s="12" t="s">
         <v>202</v>
       </c>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="94"/>
-      <c r="B76" s="89"/>
+      <c r="B76" s="96"/>
       <c r="C76" s="12" t="s">
         <v>210</v>
       </c>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="94"/>
-      <c r="B77" s="89"/>
+      <c r="B77" s="96"/>
       <c r="C77" s="12" t="s">
         <v>251</v>
       </c>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="94"/>
-      <c r="B78" s="89"/>
+      <c r="B78" s="96"/>
       <c r="C78" s="12" t="s">
         <v>216</v>
       </c>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="94"/>
-      <c r="B79" s="89"/>
+      <c r="B79" s="96"/>
       <c r="C79" s="12" t="s">
         <v>241</v>
       </c>
@@ -3859,14 +3859,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
-      <c r="B80" s="91"/>
+      <c r="A80" s="97"/>
+      <c r="B80" s="105"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="96" t="s">
+      <c r="B81" s="95" t="s">
         <v>87</v>
       </c>
       <c r="C81" s="28" t="s">
@@ -3882,7 +3882,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="93"/>
-      <c r="B82" s="97"/>
+      <c r="B82" s="90"/>
       <c r="C82" s="55" t="s">
         <v>293</v>
       </c>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="94"/>
-      <c r="B83" s="98"/>
+      <c r="B83" s="89"/>
       <c r="C83" s="12" t="s">
         <v>196</v>
       </c>
@@ -3910,12 +3910,12 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="94"/>
-      <c r="B84" s="99"/>
+      <c r="B84" s="91"/>
       <c r="E84" s="35"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="94"/>
-      <c r="B85" s="100" t="s">
+      <c r="B85" s="88" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="37" t="s">
@@ -3931,7 +3931,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="94"/>
-      <c r="B86" s="98"/>
+      <c r="B86" s="89"/>
       <c r="C86" s="12" t="s">
         <v>197</v>
       </c>
@@ -3945,7 +3945,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="94"/>
-      <c r="B87" s="99"/>
+      <c r="B87" s="91"/>
       <c r="C87" s="39"/>
       <c r="D87" s="39"/>
       <c r="E87" s="40"/>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="94"/>
-      <c r="B88" s="100" t="s">
+      <c r="B88" s="88" t="s">
         <v>94</v>
       </c>
       <c r="C88" s="12" t="s">
@@ -3969,7 +3969,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="94"/>
-      <c r="B89" s="98"/>
+      <c r="B89" s="89"/>
       <c r="C89" s="12" t="s">
         <v>198</v>
       </c>
@@ -3982,8 +3982,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="95"/>
-      <c r="B90" s="102"/>
+      <c r="A90" s="97"/>
+      <c r="B90" s="100"/>
       <c r="C90" s="43"/>
       <c r="D90" s="43"/>
       <c r="E90" s="44"/>
@@ -3993,7 +3993,7 @@
       <c r="A91" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="B91" s="96" t="s">
+      <c r="B91" s="95" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="28" t="s">
@@ -4009,7 +4009,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="93"/>
-      <c r="B92" s="98"/>
+      <c r="B92" s="89"/>
       <c r="C92" s="12" t="s">
         <v>225</v>
       </c>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="93"/>
-      <c r="B93" s="99"/>
+      <c r="B93" s="91"/>
       <c r="C93" s="39"/>
       <c r="D93" s="39"/>
       <c r="E93" s="39"/>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="93"/>
-      <c r="B94" s="100" t="s">
+      <c r="B94" s="88" t="s">
         <v>235</v>
       </c>
       <c r="C94" s="12" t="s">
@@ -4045,7 +4045,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="93"/>
-      <c r="B95" s="98"/>
+      <c r="B95" s="89"/>
       <c r="C95" s="12" t="s">
         <v>233</v>
       </c>
@@ -4058,7 +4058,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="93"/>
-      <c r="B96" s="98"/>
+      <c r="B96" s="89"/>
       <c r="C96" s="12" t="s">
         <v>229</v>
       </c>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="93"/>
-      <c r="B97" s="98"/>
+      <c r="B97" s="89"/>
       <c r="C97" s="12" t="s">
         <v>231</v>
       </c>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="93"/>
-      <c r="B98" s="98"/>
+      <c r="B98" s="89"/>
       <c r="C98" s="12" t="s">
         <v>234</v>
       </c>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="93"/>
-      <c r="B99" s="98"/>
+      <c r="B99" s="89"/>
       <c r="C99" s="12" t="s">
         <v>244</v>
       </c>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="93"/>
-      <c r="B100" s="100" t="s">
+      <c r="B100" s="88" t="s">
         <v>265</v>
       </c>
       <c r="C100" s="37" t="s">
@@ -4126,7 +4126,7 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="93"/>
-      <c r="B101" s="97"/>
+      <c r="B101" s="90"/>
       <c r="C101" s="55" t="s">
         <v>261</v>
       </c>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="93"/>
-      <c r="B102" s="97"/>
+      <c r="B102" s="90"/>
       <c r="C102" s="55" t="s">
         <v>276</v>
       </c>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="93"/>
-      <c r="B103" s="97"/>
+      <c r="B103" s="90"/>
       <c r="C103" s="55" t="s">
         <v>262</v>
       </c>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="93"/>
-      <c r="B104" s="97"/>
+      <c r="B104" s="90"/>
       <c r="C104" s="55" t="s">
         <v>278</v>
       </c>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="93"/>
-      <c r="B105" s="97"/>
+      <c r="B105" s="90"/>
       <c r="C105" s="55" t="s">
         <v>282</v>
       </c>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="93"/>
-      <c r="B106" s="97"/>
+      <c r="B106" s="90"/>
       <c r="C106" s="55" t="s">
         <v>259</v>
       </c>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="93"/>
-      <c r="B107" s="97"/>
+      <c r="B107" s="90"/>
       <c r="C107" s="55" t="s">
         <v>263</v>
       </c>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="93"/>
-      <c r="B108" s="97"/>
+      <c r="B108" s="90"/>
       <c r="C108" s="55" t="s">
         <v>264</v>
       </c>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="93"/>
-      <c r="B109" s="100" t="s">
+      <c r="B109" s="88" t="s">
         <v>283</v>
       </c>
       <c r="C109" s="37" t="s">
@@ -4254,7 +4254,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="93"/>
-      <c r="B110" s="97"/>
+      <c r="B110" s="90"/>
       <c r="C110" s="55" t="s">
         <v>286</v>
       </c>
@@ -4268,7 +4268,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="93"/>
-      <c r="B111" s="97"/>
+      <c r="B111" s="90"/>
       <c r="C111" s="55" t="s">
         <v>288</v>
       </c>
@@ -4282,7 +4282,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="93"/>
-      <c r="B112" s="97"/>
+      <c r="B112" s="90"/>
       <c r="C112" s="12" t="s">
         <v>289</v>
       </c>
@@ -4295,11 +4295,11 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="93"/>
-      <c r="B113" s="99"/>
+      <c r="B113" s="91"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="93"/>
-      <c r="B114" s="100" t="s">
+      <c r="B114" s="88" t="s">
         <v>294</v>
       </c>
       <c r="C114" s="37" t="s">
@@ -4315,7 +4315,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="93"/>
-      <c r="B115" s="98"/>
+      <c r="B115" s="89"/>
       <c r="C115" s="12" t="s">
         <v>297</v>
       </c>
@@ -4331,6 +4331,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="A81:A90"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="B85:B87"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="B109:B113"/>
     <mergeCell ref="A91:A116"/>
@@ -4347,12 +4353,6 @@
     <mergeCell ref="B100:B108"/>
     <mergeCell ref="B91:B93"/>
     <mergeCell ref="A55:A80"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="B71:B80"/>
-    <mergeCell ref="A81:A90"/>
-    <mergeCell ref="B81:B84"/>
-    <mergeCell ref="B85:B87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Höchst/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_HB_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEE9695-3B9B-47E4-906C-62E0B154718A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B17452-D7BA-4B74-8401-6A40B00FE3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -505,9 +505,6 @@
     <t>€/kWa</t>
   </si>
   <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
     <t>(%_Kapa)/h</t>
   </si>
   <si>
@@ -865,9 +862,6 @@
     <t>kW_el</t>
   </si>
   <si>
-    <t>€ h / kg a</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -1076,6 +1070,12 @@
   </si>
   <si>
     <t>€/a per kg_NH3/h</t>
+  </si>
+  <si>
+    <t>€/ kg a</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1088,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1140,13 +1140,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1263,7 +1256,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1292,7 +1285,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1315,8 +1307,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1330,20 +1320,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1392,17 +1382,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1413,38 +1412,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1804,10 +1794,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="81" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1824,8 +1814,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="74"/>
-      <c r="B3" s="85"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="82"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1836,12 +1826,12 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="74"/>
-      <c r="B4" s="85"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="82"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1856,8 +1846,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="74"/>
-      <c r="B5" s="85"/>
+      <c r="A5" s="71"/>
+      <c r="B5" s="82"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1872,8 +1862,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="74"/>
-      <c r="B6" s="85"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="82"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1888,8 +1878,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="74"/>
-      <c r="B7" s="85"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="82"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1904,8 +1894,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="74"/>
-      <c r="B8" s="86" t="s">
+      <c r="A8" s="71"/>
+      <c r="B8" s="83" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1922,8 +1912,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="74"/>
-      <c r="B9" s="85"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="82"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -1938,41 +1928,41 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="74"/>
-      <c r="B10" s="85"/>
+      <c r="A10" s="71"/>
+      <c r="B10" s="82"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="67">
         <v>0</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="67" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="74"/>
-      <c r="B11" s="85"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="82"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="71">
+      <c r="E11" s="68">
         <f>0.05*9070</f>
         <v>453.5</v>
       </c>
-      <c r="F11" s="72" t="s">
-        <v>309</v>
+      <c r="F11" s="69" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="74"/>
-      <c r="B12" s="85"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="82"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -1987,8 +1977,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="74"/>
-      <c r="B13" s="85"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="82"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -2003,8 +1993,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="74"/>
-      <c r="B14" s="85"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="82"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -2019,8 +2009,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="74"/>
-      <c r="B15" s="87"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -2035,8 +2025,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="74"/>
-      <c r="B16" s="78" t="s">
+      <c r="A16" s="71"/>
+      <c r="B16" s="75" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -2054,8 +2044,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="74"/>
-      <c r="B17" s="78"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="75"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
@@ -2070,8 +2060,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="74"/>
-      <c r="B18" s="78"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="75"/>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -2086,8 +2076,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="74"/>
-      <c r="B19" s="78"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="75"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -2102,8 +2092,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="74"/>
-      <c r="B20" s="78"/>
+      <c r="A20" s="71"/>
+      <c r="B20" s="75"/>
       <c r="C20" t="s">
         <v>17</v>
       </c>
@@ -2118,10 +2108,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="74" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2133,13 +2123,13 @@
       <c r="E21" s="23">
         <v>490</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>119</v>
+      <c r="F21" s="27" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="74"/>
-      <c r="B22" s="78"/>
+      <c r="A22" s="71"/>
+      <c r="B22" s="75"/>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -2154,8 +2144,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="74"/>
-      <c r="B23" s="78"/>
+      <c r="A23" s="71"/>
+      <c r="B23" s="75"/>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -2170,24 +2160,24 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="74"/>
-      <c r="B24" s="78"/>
+      <c r="A24" s="71"/>
+      <c r="B24" s="75"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
       <c r="D24" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="47">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="74"/>
-      <c r="B25" s="78"/>
+      <c r="A25" s="71"/>
+      <c r="B25" s="75"/>
       <c r="C25" t="s">
         <v>47</v>
       </c>
@@ -2202,8 +2192,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="74"/>
-      <c r="B26" s="78"/>
+      <c r="A26" s="71"/>
+      <c r="B26" s="75"/>
       <c r="C26" t="s">
         <v>48</v>
       </c>
@@ -2218,8 +2208,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="74"/>
-      <c r="B27" s="78"/>
+      <c r="A27" s="71"/>
+      <c r="B27" s="75"/>
       <c r="C27" t="s">
         <v>17</v>
       </c>
@@ -2234,8 +2224,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="74"/>
-      <c r="B28" s="78"/>
+      <c r="A28" s="71"/>
+      <c r="B28" s="75"/>
       <c r="C28" t="s">
         <v>114</v>
       </c>
@@ -2246,13 +2236,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="74"/>
-      <c r="B29" s="79" t="s">
-        <v>258</v>
+      <c r="A29" s="71"/>
+      <c r="B29" s="76" t="s">
+        <v>256</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>117</v>
@@ -2264,141 +2254,141 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="74"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="51" t="s">
+      <c r="A30" s="71"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="51" t="s">
+      <c r="D30" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="49">
         <f>E31*4</f>
         <v>424</v>
       </c>
-      <c r="F30" s="51" t="s">
+      <c r="F30" s="48" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="74"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="51" t="s">
+      <c r="A31" s="71"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="51" t="s">
+      <c r="D31" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="49">
         <v>106</v>
       </c>
-      <c r="F31" s="51" t="s">
+      <c r="F31" s="48" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="74"/>
-      <c r="B32" s="82"/>
-      <c r="C32" s="51" t="s">
+      <c r="A32" s="71"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="51" t="s">
+      <c r="D32" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="53">
+      <c r="E32" s="50">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="48" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="74"/>
-      <c r="B33" s="82"/>
-      <c r="C33" s="51" t="s">
+      <c r="A33" s="71"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="51" t="s">
+      <c r="D33" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="53">
+      <c r="E33" s="50">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F33" s="51" t="s">
+      <c r="F33" s="48" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="74"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="51" t="s">
+      <c r="A34" s="71"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="51" t="s">
+      <c r="D34" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="E34" s="53">
+      <c r="E34" s="50">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="F34" s="48" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="74"/>
-      <c r="B35" s="82"/>
-      <c r="C35" s="51" t="s">
+      <c r="A35" s="71"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="52">
+      <c r="E35" s="49">
         <v>0.25</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="48" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="74"/>
-      <c r="B36" s="82"/>
-      <c r="C36" s="51" t="s">
+      <c r="A36" s="71"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="51" t="s">
+      <c r="D36" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="E36" s="53">
+      <c r="E36" s="50">
         <v>0</v>
       </c>
-      <c r="F36" s="51" t="s">
-        <v>121</v>
+      <c r="F36" s="48" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="74"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="51" t="s">
+      <c r="A37" s="71"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="51" t="s">
+      <c r="D37" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="54">
+      <c r="E37" s="51">
         <v>15</v>
       </c>
-      <c r="F37" s="51" t="s">
+      <c r="F37" s="48" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="75"/>
-      <c r="B38" s="83"/>
+      <c r="A38" s="72"/>
+      <c r="B38" s="80"/>
       <c r="C38" s="14" t="s">
         <v>17</v>
       </c>
@@ -2413,64 +2403,64 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="70" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="57" t="s">
+      <c r="B39" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="58" t="s">
+      <c r="D39" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="59">
+      <c r="E39" s="56">
         <v>0.1699</v>
       </c>
-      <c r="F39" s="58" t="s">
+      <c r="F39" s="55" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="76"/>
-      <c r="B40" s="67" t="s">
+      <c r="A40" s="73"/>
+      <c r="B40" s="64" t="s">
+        <v>300</v>
+      </c>
+      <c r="C40" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="D40" s="65" t="s">
         <v>302</v>
       </c>
-      <c r="C40" s="68" t="s">
-        <v>303</v>
-      </c>
-      <c r="D40" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="E40" s="69">
+      <c r="E40" s="66">
         <v>0.2</v>
       </c>
-      <c r="F40" s="68" t="s">
-        <v>271</v>
+      <c r="F40" s="65" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="76"/>
-      <c r="B41" s="60" t="s">
+      <c r="A41" s="73"/>
+      <c r="B41" s="57" t="s">
+        <v>297</v>
+      </c>
+      <c r="C41" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="D41" s="58" t="s">
         <v>299</v>
       </c>
-      <c r="C41" s="61" t="s">
-        <v>300</v>
-      </c>
-      <c r="D41" s="61" t="s">
-        <v>301</v>
-      </c>
-      <c r="E41" s="62">
+      <c r="E41" s="59">
         <v>5</v>
       </c>
-      <c r="F41" s="61" t="s">
-        <v>271</v>
+      <c r="F41" s="58" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="74"/>
-      <c r="B42" s="79" t="s">
+      <c r="A42" s="71"/>
+      <c r="B42" s="76" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2487,8 +2477,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="74"/>
-      <c r="B43" s="78"/>
+      <c r="A43" s="71"/>
+      <c r="B43" s="75"/>
       <c r="C43" t="s">
         <v>12</v>
       </c>
@@ -2503,8 +2493,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="74"/>
-      <c r="B44" s="78"/>
+      <c r="A44" s="71"/>
+      <c r="B44" s="75"/>
       <c r="C44" t="s">
         <v>19</v>
       </c>
@@ -2519,8 +2509,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="74"/>
-      <c r="B45" s="78"/>
+      <c r="A45" s="71"/>
+      <c r="B45" s="75"/>
       <c r="C45" t="s">
         <v>20</v>
       </c>
@@ -2535,8 +2525,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="74"/>
-      <c r="B46" s="78"/>
+      <c r="A46" s="71"/>
+      <c r="B46" s="75"/>
       <c r="C46" t="s">
         <v>15</v>
       </c>
@@ -2551,8 +2541,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="74"/>
-      <c r="B47" s="78"/>
+      <c r="A47" s="71"/>
+      <c r="B47" s="75"/>
       <c r="C47" t="s">
         <v>82</v>
       </c>
@@ -2567,8 +2557,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="74"/>
-      <c r="B48" s="80"/>
+      <c r="A48" s="71"/>
+      <c r="B48" s="77"/>
       <c r="C48" s="5" t="s">
         <v>17</v>
       </c>
@@ -2583,8 +2573,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="74"/>
-      <c r="B49" s="79" t="s">
+      <c r="A49" s="71"/>
+      <c r="B49" s="76" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -2601,8 +2591,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="74"/>
-      <c r="B50" s="78"/>
+      <c r="A50" s="71"/>
+      <c r="B50" s="75"/>
       <c r="C50" t="s">
         <v>12</v>
       </c>
@@ -2617,15 +2607,15 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="74"/>
-      <c r="B51" s="78"/>
+      <c r="A51" s="71"/>
+      <c r="B51" s="75"/>
       <c r="C51" t="s">
         <v>19</v>
       </c>
       <c r="D51" t="s">
         <v>64</v>
       </c>
-      <c r="E51" s="45">
+      <c r="E51" s="44">
         <v>12.68</v>
       </c>
       <c r="F51" s="25" t="s">
@@ -2633,15 +2623,15 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="74"/>
-      <c r="B52" s="78"/>
+      <c r="A52" s="71"/>
+      <c r="B52" s="75"/>
       <c r="C52" t="s">
         <v>20</v>
       </c>
       <c r="D52" t="s">
         <v>61</v>
       </c>
-      <c r="E52" s="49">
+      <c r="E52" s="46">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F52" t="s">
@@ -2649,8 +2639,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="74"/>
-      <c r="B53" s="78"/>
+      <c r="A53" s="71"/>
+      <c r="B53" s="75"/>
       <c r="C53" t="s">
         <v>15</v>
       </c>
@@ -2665,15 +2655,15 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="74"/>
-      <c r="B54" s="78"/>
+      <c r="A54" s="71"/>
+      <c r="B54" s="75"/>
       <c r="C54" t="s">
         <v>82</v>
       </c>
       <c r="D54" t="s">
         <v>79</v>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="26">
         <v>1000000</v>
       </c>
       <c r="F54" t="s">
@@ -2681,8 +2671,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="75"/>
-      <c r="B55" s="81"/>
+      <c r="A55" s="72"/>
+      <c r="B55" s="78"/>
       <c r="C55" s="14" t="s">
         <v>17</v>
       </c>
@@ -2697,7 +2687,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="73" t="s">
+      <c r="A56" s="70" t="s">
         <v>90</v>
       </c>
       <c r="B56" s="16" t="s">
@@ -2717,7 +2707,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="74"/>
+      <c r="A57" s="71"/>
       <c r="B57" s="17" t="s">
         <v>93</v>
       </c>
@@ -2735,7 +2725,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
+      <c r="A58" s="72"/>
       <c r="B58" s="1" t="s">
         <v>94</v>
       </c>
@@ -2787,22 +2777,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="29" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2810,1517 +2800,1517 @@
       <c r="A2" s="92" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="E2" s="31"/>
+      <c r="F2" s="27" t="s">
         <v>124</v>
-      </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="28" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="94"/>
-      <c r="B3" s="89"/>
+      <c r="B3" s="98"/>
       <c r="C3" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E3" s="33"/>
+        <v>143</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="94"/>
-      <c r="B4" s="89"/>
+      <c r="B4" s="98"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="34"/>
+        <v>152</v>
+      </c>
+      <c r="E4" s="33"/>
       <c r="F4" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="94"/>
-      <c r="B5" s="89"/>
+      <c r="B5" s="98"/>
       <c r="C5" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" s="35"/>
+        <v>170</v>
+      </c>
+      <c r="E5" s="34"/>
       <c r="F5" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="94"/>
-      <c r="B6" s="89"/>
+      <c r="B6" s="98"/>
       <c r="C6" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="36"/>
+        <v>185</v>
+      </c>
+      <c r="E6" s="35"/>
       <c r="F6" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="94"/>
-      <c r="B7" s="89"/>
+      <c r="B7" s="98"/>
       <c r="C7" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="E7" s="36"/>
+        <v>204</v>
+      </c>
+      <c r="E7" s="35"/>
       <c r="F7" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="94"/>
-      <c r="B8" s="89"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="E8" s="36"/>
+        <v>248</v>
+      </c>
+      <c r="E8" s="35"/>
       <c r="F8" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="94"/>
-      <c r="B9" s="89"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E9" s="36"/>
+        <v>214</v>
+      </c>
+      <c r="E9" s="35"/>
       <c r="F9" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="94"/>
-      <c r="B10" s="89"/>
+      <c r="B10" s="98"/>
       <c r="C10" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="36"/>
+        <v>247</v>
+      </c>
+      <c r="E10" s="35"/>
       <c r="F10" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="94"/>
-      <c r="B11" s="89"/>
-      <c r="E11" s="35"/>
+      <c r="B11" s="98"/>
+      <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="94"/>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="37" t="s">
+      <c r="C12" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="37"/>
+      <c r="F12" s="36" t="s">
         <v>132</v>
-      </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="37" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="94"/>
-      <c r="B13" s="89"/>
+      <c r="B13" s="98"/>
       <c r="C13" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="E13" s="33"/>
+        <v>175</v>
+      </c>
+      <c r="E13" s="32"/>
       <c r="F13" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="94"/>
-      <c r="B14" s="89"/>
+      <c r="B14" s="98"/>
       <c r="C14" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33" t="s">
-        <v>164</v>
+        <v>177</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="94"/>
-      <c r="B15" s="89"/>
+      <c r="B15" s="98"/>
       <c r="C15" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="E15" s="35"/>
+        <v>178</v>
+      </c>
+      <c r="E15" s="34"/>
       <c r="F15" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="94"/>
-      <c r="B16" s="89"/>
+      <c r="B16" s="98"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="E16" s="33"/>
+        <v>181</v>
+      </c>
+      <c r="E16" s="32"/>
       <c r="F16" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="94"/>
-      <c r="B17" s="89"/>
+      <c r="B17" s="98"/>
       <c r="C17" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="E17" s="33"/>
+        <v>190</v>
+      </c>
+      <c r="E17" s="32"/>
       <c r="F17" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="94"/>
-      <c r="B18" s="89"/>
+      <c r="B18" s="98"/>
       <c r="C18" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" s="36"/>
+        <v>207</v>
+      </c>
+      <c r="E18" s="35"/>
       <c r="F18" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="94"/>
-      <c r="B19" s="89"/>
+      <c r="B19" s="98"/>
       <c r="C19" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" s="36"/>
+        <v>254</v>
+      </c>
+      <c r="E19" s="35"/>
       <c r="F19" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="94"/>
-      <c r="B20" s="89"/>
+      <c r="B20" s="98"/>
       <c r="C20" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="E20" s="36"/>
+        <v>221</v>
+      </c>
+      <c r="E20" s="35"/>
       <c r="F20" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="94"/>
-      <c r="B21" s="89"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E21" s="36"/>
+        <v>246</v>
+      </c>
+      <c r="E21" s="35"/>
       <c r="F21" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="94"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="39"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="94"/>
-      <c r="B23" s="96" t="s">
+      <c r="B23" s="89" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" s="33"/>
+        <v>130</v>
+      </c>
+      <c r="E23" s="32"/>
       <c r="F23" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="94"/>
-      <c r="B24" s="96"/>
+      <c r="B24" s="89"/>
       <c r="C24" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="33"/>
+        <v>144</v>
+      </c>
+      <c r="E24" s="32"/>
       <c r="F24" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="94"/>
-      <c r="B25" s="96"/>
+      <c r="B25" s="89"/>
       <c r="C25" s="12" t="s">
         <v>102</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25" s="35"/>
+        <v>153</v>
+      </c>
+      <c r="E25" s="34"/>
       <c r="F25" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="94"/>
-      <c r="B26" s="96"/>
+      <c r="B26" s="89"/>
       <c r="C26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" s="35"/>
+      <c r="F26" s="12" t="s">
         <v>174</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="12" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="94"/>
-      <c r="B27" s="96"/>
+      <c r="B27" s="89"/>
       <c r="C27" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="E27" s="36"/>
+        <v>188</v>
+      </c>
+      <c r="E27" s="35"/>
       <c r="F27" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="94"/>
-      <c r="B28" s="96"/>
+      <c r="B28" s="89"/>
       <c r="C28" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="E28" s="36"/>
+        <v>205</v>
+      </c>
+      <c r="E28" s="35"/>
       <c r="F28" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="94"/>
-      <c r="B29" s="96"/>
+      <c r="B29" s="89"/>
       <c r="C29" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="36"/>
+        <v>252</v>
+      </c>
+      <c r="E29" s="35"/>
       <c r="F29" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="94"/>
-      <c r="B30" s="96"/>
+      <c r="B30" s="89"/>
       <c r="C30" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E30" s="35"/>
+        <v>219</v>
+      </c>
+      <c r="E30" s="34"/>
       <c r="F30" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="94"/>
-      <c r="B31" s="96"/>
+      <c r="B31" s="89"/>
       <c r="C31" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="E31" s="35"/>
+        <v>245</v>
+      </c>
+      <c r="E31" s="34"/>
       <c r="F31" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="94"/>
-      <c r="B32" s="96"/>
-      <c r="E32" s="35"/>
+      <c r="B32" s="89"/>
+      <c r="E32" s="34"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="98" t="s">
+      <c r="B33" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="47" t="s">
-        <v>239</v>
+      <c r="C33" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="40"/>
+      <c r="F33" s="27" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="94"/>
-      <c r="B34" s="96"/>
+      <c r="B34" s="89"/>
       <c r="C34" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="48" t="s">
-        <v>38</v>
+        <v>138</v>
+      </c>
+      <c r="E34" s="34"/>
+      <c r="F34" s="12" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="94"/>
-      <c r="B35" s="96"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E35" s="36"/>
+        <v>166</v>
+      </c>
+      <c r="E35" s="35"/>
       <c r="F35" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="94"/>
-      <c r="B36" s="96"/>
+      <c r="B36" s="89"/>
       <c r="C36" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E36" s="35"/>
+        <v>167</v>
+      </c>
+      <c r="E36" s="34"/>
       <c r="F36" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="94"/>
-      <c r="B37" s="96"/>
+      <c r="B37" s="89"/>
       <c r="C37" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E37" s="35"/>
+        <v>189</v>
+      </c>
+      <c r="E37" s="34"/>
       <c r="F37" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="94"/>
-      <c r="B38" s="96"/>
+      <c r="B38" s="89"/>
       <c r="C38" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E38" s="35"/>
+        <v>206</v>
+      </c>
+      <c r="E38" s="34"/>
       <c r="F38" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="94"/>
-      <c r="B39" s="96"/>
+      <c r="B39" s="89"/>
       <c r="C39" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="E39" s="35"/>
+        <v>253</v>
+      </c>
+      <c r="E39" s="34"/>
       <c r="F39" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="94"/>
-      <c r="B40" s="96"/>
+      <c r="B40" s="89"/>
       <c r="C40" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="E40" s="35"/>
+        <v>220</v>
+      </c>
+      <c r="E40" s="34"/>
       <c r="F40" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="94"/>
-      <c r="B41" s="96"/>
+      <c r="B41" s="89"/>
       <c r="C41" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="E41" s="35"/>
+        <v>244</v>
+      </c>
+      <c r="E41" s="34"/>
       <c r="F41" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="94"/>
-      <c r="B42" s="96"/>
-      <c r="E42" s="35"/>
+      <c r="B42" s="89"/>
+      <c r="E42" s="34"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="94"/>
-      <c r="B43" s="99" t="s">
+      <c r="B43" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" s="42"/>
-      <c r="F43" s="37" t="s">
-        <v>125</v>
+      <c r="C43" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" s="41"/>
+      <c r="F43" s="36" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="94"/>
-      <c r="B44" s="96"/>
+      <c r="B44" s="89"/>
       <c r="C44" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" s="35"/>
+        <v>128</v>
+      </c>
+      <c r="E44" s="34"/>
       <c r="F44" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="94"/>
-      <c r="B45" s="89"/>
+      <c r="B45" s="98"/>
       <c r="C45" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" s="33"/>
+      <c r="E45" s="32"/>
       <c r="F45" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="94"/>
-      <c r="B46" s="89"/>
+      <c r="B46" s="98"/>
       <c r="C46" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="E46" s="33"/>
+        <v>236</v>
+      </c>
+      <c r="E46" s="32"/>
       <c r="F46" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="94"/>
-      <c r="B47" s="89"/>
+      <c r="B47" s="98"/>
       <c r="C47" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="E47" s="33"/>
+        <v>154</v>
+      </c>
+      <c r="E47" s="32"/>
       <c r="F47" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="94"/>
-      <c r="B48" s="89"/>
+      <c r="B48" s="98"/>
       <c r="C48" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="E48" s="35"/>
+        <v>155</v>
+      </c>
+      <c r="E48" s="34"/>
       <c r="F48" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="94"/>
-      <c r="B49" s="89"/>
+      <c r="B49" s="98"/>
       <c r="C49" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E49" s="33"/>
+        <v>187</v>
+      </c>
+      <c r="E49" s="32"/>
       <c r="F49" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="94"/>
-      <c r="B50" s="89"/>
+      <c r="B50" s="98"/>
       <c r="C50" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="E50" s="35"/>
+        <v>203</v>
+      </c>
+      <c r="E50" s="34"/>
       <c r="F50" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="94"/>
-      <c r="B51" s="89"/>
+      <c r="B51" s="98"/>
       <c r="C51" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E51" s="35"/>
+        <v>255</v>
+      </c>
+      <c r="E51" s="34"/>
       <c r="F51" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="94"/>
-      <c r="B52" s="89"/>
+      <c r="B52" s="98"/>
       <c r="C52" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" s="35"/>
+        <v>218</v>
+      </c>
+      <c r="E52" s="34"/>
       <c r="F52" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="94"/>
-      <c r="B53" s="89"/>
+      <c r="B53" s="98"/>
       <c r="C53" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="E53" s="35"/>
+        <v>243</v>
+      </c>
+      <c r="E53" s="34"/>
       <c r="F53" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
-      <c r="B54" s="100"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="43"/>
+      <c r="A54" s="95"/>
+      <c r="B54" s="102"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="42"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="95" t="s">
+      <c r="B55" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C55" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" s="40"/>
+      <c r="F55" s="27" t="s">
         <v>147</v>
-      </c>
-      <c r="D55" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="E55" s="41"/>
-      <c r="F55" s="28" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="94"/>
-      <c r="B56" s="89"/>
+      <c r="B56" s="98"/>
       <c r="C56" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="E56" s="33"/>
+        <v>198</v>
+      </c>
+      <c r="E56" s="32"/>
       <c r="F56" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="94"/>
-      <c r="B57" s="91"/>
-      <c r="E57" s="33"/>
+      <c r="B57" s="99"/>
+      <c r="E57" s="32"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="94"/>
-      <c r="B58" s="101" t="s">
+      <c r="B58" s="85" t="s">
+        <v>303</v>
+      </c>
+      <c r="C58" s="60" t="s">
+        <v>304</v>
+      </c>
+      <c r="D58" s="60" t="s">
         <v>305</v>
       </c>
-      <c r="C58" s="63" t="s">
-        <v>306</v>
-      </c>
-      <c r="D58" s="63" t="s">
-        <v>307</v>
-      </c>
-      <c r="E58" s="64"/>
-      <c r="F58" s="63" t="s">
-        <v>175</v>
+      <c r="E58" s="61"/>
+      <c r="F58" s="60" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="94"/>
-      <c r="B59" s="102"/>
-      <c r="C59" s="65" t="s">
-        <v>200</v>
-      </c>
-      <c r="D59" s="65" t="s">
-        <v>308</v>
-      </c>
-      <c r="E59" s="66"/>
-      <c r="F59" s="65" t="s">
-        <v>195</v>
+      <c r="B59" s="86"/>
+      <c r="C59" s="62" t="s">
+        <v>199</v>
+      </c>
+      <c r="D59" s="62" t="s">
+        <v>306</v>
+      </c>
+      <c r="E59" s="63"/>
+      <c r="F59" s="62" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="94"/>
-      <c r="B60" s="103"/>
-      <c r="C60" s="65"/>
-      <c r="D60" s="65"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="65"/>
+      <c r="B60" s="87"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="62"/>
+      <c r="E60" s="63"/>
+      <c r="F60" s="62"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="94"/>
-      <c r="B61" s="99" t="s">
+      <c r="B61" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D61" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="E61" s="42"/>
-      <c r="F61" s="37" t="s">
+      <c r="C61" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="36" t="s">
         <v>125</v>
+      </c>
+      <c r="E61" s="41"/>
+      <c r="F61" s="36" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="94"/>
-      <c r="B62" s="96"/>
+      <c r="B62" s="89"/>
       <c r="C62" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E62" s="45"/>
+        <v>137</v>
+      </c>
+      <c r="E62" s="44"/>
       <c r="F62" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="94"/>
-      <c r="B63" s="96"/>
+      <c r="B63" s="89"/>
       <c r="C63" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E63" s="45"/>
+        <v>150</v>
+      </c>
+      <c r="E63" s="44"/>
       <c r="F63" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="94"/>
-      <c r="B64" s="96"/>
+      <c r="B64" s="89"/>
       <c r="C64" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="E64" s="33"/>
+        <v>186</v>
+      </c>
+      <c r="E64" s="32"/>
       <c r="F64" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="94"/>
-      <c r="B65" s="96"/>
+      <c r="B65" s="89"/>
       <c r="C65" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D65" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="E65" s="36"/>
+      <c r="E65" s="35"/>
       <c r="F65" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="94"/>
-      <c r="B66" s="96"/>
+      <c r="B66" s="89"/>
       <c r="C66" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="D66" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="E66" s="33"/>
+      <c r="E66" s="32"/>
       <c r="F66" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="94"/>
-      <c r="B67" s="96"/>
+      <c r="B67" s="89"/>
       <c r="C67" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="E67" s="33"/>
+      <c r="E67" s="32"/>
       <c r="F67" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="94"/>
-      <c r="B68" s="96"/>
+      <c r="B68" s="89"/>
       <c r="C68" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="E68" s="35"/>
+        <v>217</v>
+      </c>
+      <c r="E68" s="34"/>
       <c r="F68" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="94"/>
-      <c r="B69" s="96"/>
+      <c r="B69" s="89"/>
       <c r="C69" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="D69" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="E69" s="35"/>
+      <c r="E69" s="34"/>
       <c r="F69" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="94"/>
-      <c r="B70" s="104"/>
+      <c r="B70" s="90"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="94"/>
-      <c r="B71" s="99" t="s">
+      <c r="B71" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="E71" s="42"/>
-      <c r="F71" s="37" t="s">
-        <v>125</v>
+      <c r="C71" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="E71" s="41"/>
+      <c r="F71" s="36" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="94"/>
-      <c r="B72" s="96"/>
+      <c r="B72" s="89"/>
       <c r="C72" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E72" s="45"/>
+        <v>134</v>
+      </c>
+      <c r="E72" s="44"/>
       <c r="F72" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="94"/>
-      <c r="B73" s="96"/>
+      <c r="B73" s="89"/>
       <c r="C73" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E73" s="45"/>
+        <v>148</v>
+      </c>
+      <c r="E73" s="44"/>
       <c r="F73" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="94"/>
-      <c r="B74" s="96"/>
+      <c r="B74" s="89"/>
       <c r="C74" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D74" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E74" s="45"/>
+      <c r="E74" s="44"/>
       <c r="F74" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="94"/>
-      <c r="B75" s="96"/>
+      <c r="B75" s="89"/>
       <c r="C75" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="E75" s="36"/>
+        <v>200</v>
+      </c>
+      <c r="E75" s="35"/>
       <c r="F75" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="94"/>
-      <c r="B76" s="96"/>
+      <c r="B76" s="89"/>
       <c r="C76" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="E76" s="46"/>
+        <v>208</v>
+      </c>
+      <c r="E76" s="45"/>
       <c r="F76" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="94"/>
-      <c r="B77" s="96"/>
+      <c r="B77" s="89"/>
       <c r="C77" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="E77" s="46"/>
+        <v>250</v>
+      </c>
+      <c r="E77" s="45"/>
       <c r="F77" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="94"/>
-      <c r="B78" s="96"/>
+      <c r="B78" s="89"/>
       <c r="C78" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="D78" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="E78" s="35"/>
+      <c r="E78" s="34"/>
       <c r="F78" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="94"/>
-      <c r="B79" s="96"/>
+      <c r="B79" s="89"/>
       <c r="C79" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="E79" s="35"/>
+        <v>240</v>
+      </c>
+      <c r="E79" s="34"/>
       <c r="F79" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="97"/>
-      <c r="B80" s="105"/>
+      <c r="A80" s="95"/>
+      <c r="B80" s="91"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="95" t="s">
+      <c r="B81" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="C81" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="D81" s="28" t="s">
+      <c r="C81" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="E81" s="32"/>
-      <c r="F81" s="28" t="s">
-        <v>148</v>
+      <c r="D81" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E81" s="31"/>
+      <c r="F81" s="27" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="93"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="55" t="s">
-        <v>293</v>
-      </c>
-      <c r="D82" s="55" t="s">
-        <v>292</v>
-      </c>
-      <c r="E82" s="56"/>
-      <c r="F82" s="55" t="s">
-        <v>195</v>
+      <c r="B82" s="97"/>
+      <c r="C82" s="52" t="s">
+        <v>291</v>
+      </c>
+      <c r="D82" s="52" t="s">
+        <v>290</v>
+      </c>
+      <c r="E82" s="53"/>
+      <c r="F82" s="52" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="94"/>
-      <c r="B83" s="89"/>
+      <c r="B83" s="98"/>
       <c r="C83" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E83" s="35"/>
+        <v>191</v>
+      </c>
+      <c r="E83" s="34"/>
       <c r="F83" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="94"/>
-      <c r="B84" s="91"/>
-      <c r="E84" s="35"/>
+      <c r="B84" s="99"/>
+      <c r="E84" s="34"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="94"/>
-      <c r="B85" s="88" t="s">
+      <c r="B85" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="C85" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="D85" s="37" t="s">
+      <c r="C85" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="E85" s="42"/>
-      <c r="F85" s="37" t="s">
-        <v>164</v>
+      <c r="D85" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E85" s="41"/>
+      <c r="F85" s="36" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="94"/>
-      <c r="B86" s="89"/>
+      <c r="B86" s="98"/>
       <c r="C86" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E86" s="35"/>
+        <v>192</v>
+      </c>
+      <c r="E86" s="34"/>
       <c r="F86" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="94"/>
-      <c r="B87" s="91"/>
-      <c r="C87" s="39"/>
-      <c r="D87" s="39"/>
-      <c r="E87" s="40"/>
-      <c r="F87" s="39"/>
+      <c r="B87" s="99"/>
+      <c r="C87" s="38"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="38"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="94"/>
-      <c r="B88" s="88" t="s">
+      <c r="B88" s="100" t="s">
         <v>94</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D88" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E88" s="34"/>
+      <c r="F88" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="E88" s="35"/>
-      <c r="F88" s="12" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="94"/>
-      <c r="B89" s="89"/>
+      <c r="B89" s="98"/>
       <c r="C89" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D89" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E89" s="34"/>
+      <c r="F89" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="E89" s="35"/>
-      <c r="F89" s="12" t="s">
-        <v>195</v>
-      </c>
     </row>
     <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="97"/>
-      <c r="B90" s="100"/>
-      <c r="C90" s="43"/>
-      <c r="D90" s="43"/>
-      <c r="E90" s="44"/>
-      <c r="F90" s="43"/>
+      <c r="A90" s="95"/>
+      <c r="B90" s="102"/>
+      <c r="C90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="43"/>
+      <c r="F90" s="42"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="92" t="s">
-        <v>212</v>
-      </c>
-      <c r="B91" s="95" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="D91" s="28" t="s">
+      <c r="C91" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="E91" s="28"/>
-      <c r="F91" s="28" t="s">
-        <v>183</v>
+      <c r="D91" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="E91" s="27"/>
+      <c r="F91" s="27" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="93"/>
-      <c r="B92" s="89"/>
+      <c r="B92" s="98"/>
       <c r="C92" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D92" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="D92" s="12" t="s">
-        <v>226</v>
-      </c>
       <c r="F92" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="93"/>
-      <c r="B93" s="91"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="39"/>
-      <c r="F93" s="39"/>
+      <c r="B93" s="99"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="93"/>
-      <c r="B94" s="88" t="s">
-        <v>235</v>
+      <c r="B94" s="100" t="s">
+        <v>234</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="93"/>
-      <c r="B95" s="89"/>
+      <c r="B95" s="98"/>
       <c r="C95" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F95" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="93"/>
-      <c r="B96" s="89"/>
+      <c r="B96" s="98"/>
       <c r="C96" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="93"/>
-      <c r="B97" s="89"/>
+      <c r="B97" s="98"/>
       <c r="C97" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="93"/>
-      <c r="B98" s="89"/>
+      <c r="B98" s="98"/>
       <c r="C98" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="93"/>
-      <c r="B99" s="89"/>
+      <c r="B99" s="98"/>
       <c r="C99" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="93"/>
-      <c r="B100" s="88" t="s">
+      <c r="B100" s="100" t="s">
+        <v>263</v>
+      </c>
+      <c r="C100" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36" t="s">
         <v>265</v>
-      </c>
-      <c r="C100" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="D100" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="E100" s="37"/>
-      <c r="F100" s="37" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="93"/>
-      <c r="B101" s="90"/>
-      <c r="C101" s="55" t="s">
-        <v>261</v>
-      </c>
-      <c r="D101" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="E101" s="55"/>
-      <c r="F101" s="55" t="s">
+      <c r="B101" s="97"/>
+      <c r="C101" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="D101" s="52" t="s">
         <v>267</v>
+      </c>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="93"/>
-      <c r="B102" s="90"/>
-      <c r="C102" s="55" t="s">
-        <v>276</v>
-      </c>
-      <c r="D102" s="55" t="s">
-        <v>275</v>
-      </c>
-      <c r="E102" s="55"/>
-      <c r="F102" s="55" t="s">
-        <v>280</v>
+      <c r="B102" s="97"/>
+      <c r="C102" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="D102" s="52" t="s">
+        <v>273</v>
+      </c>
+      <c r="E102" s="52"/>
+      <c r="F102" s="52" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="93"/>
-      <c r="B103" s="90"/>
-      <c r="C103" s="55" t="s">
-        <v>262</v>
-      </c>
-      <c r="D103" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="E103" s="55"/>
-      <c r="F103" s="55" t="s">
-        <v>267</v>
+      <c r="B103" s="97"/>
+      <c r="C103" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="D103" s="52" t="s">
+        <v>266</v>
+      </c>
+      <c r="E103" s="52"/>
+      <c r="F103" s="52" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="93"/>
-      <c r="B104" s="90"/>
-      <c r="C104" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="D104" s="55" t="s">
+      <c r="B104" s="97"/>
+      <c r="C104" s="52" t="s">
+        <v>276</v>
+      </c>
+      <c r="D104" s="52" t="s">
+        <v>275</v>
+      </c>
+      <c r="E104" s="52"/>
+      <c r="F104" s="52" t="s">
         <v>277</v>
-      </c>
-      <c r="E104" s="55"/>
-      <c r="F104" s="55" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="93"/>
-      <c r="B105" s="90"/>
-      <c r="C105" s="55" t="s">
-        <v>282</v>
-      </c>
-      <c r="D105" s="55" t="s">
-        <v>270</v>
-      </c>
-      <c r="E105" s="55"/>
-      <c r="F105" s="55" t="s">
-        <v>271</v>
+      <c r="B105" s="97"/>
+      <c r="C105" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="D105" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="E105" s="52"/>
+      <c r="F105" s="52" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="93"/>
-      <c r="B106" s="90"/>
-      <c r="C106" s="55" t="s">
-        <v>259</v>
+      <c r="B106" s="97"/>
+      <c r="C106" s="52" t="s">
+        <v>257</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="E106" s="55"/>
-      <c r="F106" s="55" t="s">
-        <v>271</v>
+        <v>279</v>
+      </c>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="93"/>
-      <c r="B107" s="90"/>
-      <c r="C107" s="55" t="s">
-        <v>263</v>
-      </c>
-      <c r="D107" s="55" t="s">
-        <v>272</v>
-      </c>
-      <c r="E107" s="55"/>
+      <c r="B107" s="97"/>
+      <c r="C107" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="D107" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="E107" s="52"/>
       <c r="F107" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="93"/>
-      <c r="B108" s="90"/>
-      <c r="C108" s="55" t="s">
-        <v>264</v>
-      </c>
-      <c r="D108" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="E108" s="55"/>
-      <c r="F108" s="55" t="s">
-        <v>274</v>
+      <c r="B108" s="97"/>
+      <c r="C108" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="D108" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="E108" s="52"/>
+      <c r="F108" s="52" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="93"/>
-      <c r="B109" s="88" t="s">
+      <c r="B109" s="100" t="s">
+        <v>281</v>
+      </c>
+      <c r="C109" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="C109" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="D109" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="E109" s="37"/>
-      <c r="F109" s="37" t="s">
-        <v>267</v>
+      <c r="D109" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="E109" s="36"/>
+      <c r="F109" s="36" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="93"/>
-      <c r="B110" s="90"/>
-      <c r="C110" s="55" t="s">
-        <v>286</v>
-      </c>
-      <c r="D110" s="55" t="s">
-        <v>287</v>
-      </c>
-      <c r="E110" s="55"/>
-      <c r="F110" s="55" t="s">
-        <v>271</v>
+      <c r="B110" s="97"/>
+      <c r="C110" s="52" t="s">
+        <v>284</v>
+      </c>
+      <c r="D110" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="E110" s="52"/>
+      <c r="F110" s="52" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="93"/>
-      <c r="B111" s="90"/>
-      <c r="C111" s="55" t="s">
+      <c r="B111" s="97"/>
+      <c r="C111" s="52" t="s">
+        <v>286</v>
+      </c>
+      <c r="D111" s="52" t="s">
         <v>288</v>
       </c>
-      <c r="D111" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="E111" s="55"/>
-      <c r="F111" s="55" t="s">
-        <v>271</v>
+      <c r="E111" s="52"/>
+      <c r="F111" s="52" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="93"/>
-      <c r="B112" s="90"/>
+      <c r="B112" s="97"/>
       <c r="C112" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D112" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="D112" s="12" t="s">
-        <v>291</v>
-      </c>
       <c r="F112" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="93"/>
-      <c r="B113" s="91"/>
+      <c r="B113" s="99"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="93"/>
-      <c r="B114" s="88" t="s">
+      <c r="B114" s="100" t="s">
+        <v>292</v>
+      </c>
+      <c r="C114" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="D114" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="C114" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="D114" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="E114" s="37"/>
-      <c r="F114" s="37" t="s">
+      <c r="E114" s="36"/>
+      <c r="F114" s="36" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="93"/>
-      <c r="B115" s="89"/>
+      <c r="B115" s="98"/>
       <c r="C115" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>100</v>
@@ -4331,12 +4321,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="B71:B80"/>
-    <mergeCell ref="A81:A90"/>
-    <mergeCell ref="B81:B84"/>
-    <mergeCell ref="B85:B87"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="B109:B113"/>
     <mergeCell ref="A91:A116"/>
@@ -4353,6 +4337,12 @@
     <mergeCell ref="B100:B108"/>
     <mergeCell ref="B91:B93"/>
     <mergeCell ref="A55:A80"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="A81:A90"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="B85:B87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Höchst/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_HB_Höchst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_HB_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B17452-D7BA-4B74-8401-6A40B00FE3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8FB2CC-2B7F-49F5-B49F-31140357E784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1083,10 +1083,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1254,29 +1254,29 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1289,42 +1289,36 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1333,9 +1327,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1344,9 +1338,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1364,16 +1355,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1406,9 +1394,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1416,9 +1401,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1794,10 +1776,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="74" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1814,8 +1796,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="71"/>
-      <c r="B3" s="82"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="72"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1830,8 +1812,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="71"/>
-      <c r="B4" s="82"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="72"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1839,15 +1821,15 @@
         <v>28</v>
       </c>
       <c r="E4" s="20">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="71"/>
-      <c r="B5" s="82"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="72"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1862,8 +1844,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="65"/>
+      <c r="B6" s="72"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1878,8 +1860,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="71"/>
-      <c r="B7" s="82"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="72"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1894,8 +1876,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
-      <c r="B8" s="83" t="s">
+      <c r="A8" s="65"/>
+      <c r="B8" s="75" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1912,8 +1894,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
-      <c r="B9" s="82"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="72"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -1928,41 +1910,41 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="82"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="72"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="67">
+      <c r="E10" s="61">
         <v>0</v>
       </c>
-      <c r="F10" s="67" t="s">
+      <c r="F10" s="61" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="71"/>
-      <c r="B11" s="82"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="72"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="68">
+      <c r="E11" s="62">
         <f>0.05*9070</f>
         <v>453.5</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="63" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
-      <c r="B12" s="82"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="72"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -1977,8 +1959,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="82"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="72"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -1993,8 +1975,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
-      <c r="B14" s="82"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="72"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -2009,8 +1991,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
-      <c r="B15" s="84"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="76"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -2025,8 +2007,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="71"/>
-      <c r="B16" s="75" t="s">
+      <c r="A16" s="65"/>
+      <c r="B16" s="68" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -2044,8 +2026,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="71"/>
-      <c r="B17" s="75"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="68"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
@@ -2060,8 +2042,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="71"/>
-      <c r="B18" s="75"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="68"/>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -2076,8 +2058,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="71"/>
-      <c r="B19" s="75"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="68"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -2092,8 +2074,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="71"/>
-      <c r="B20" s="75"/>
+      <c r="A20" s="65"/>
+      <c r="B20" s="68"/>
       <c r="C20" t="s">
         <v>17</v>
       </c>
@@ -2108,10 +2090,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="67" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2128,8 +2110,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="71"/>
-      <c r="B22" s="75"/>
+      <c r="A22" s="65"/>
+      <c r="B22" s="68"/>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -2144,8 +2126,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="71"/>
-      <c r="B23" s="75"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="68"/>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -2160,8 +2142,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="71"/>
-      <c r="B24" s="75"/>
+      <c r="A24" s="65"/>
+      <c r="B24" s="68"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
@@ -2176,8 +2158,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="71"/>
-      <c r="B25" s="75"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="68"/>
       <c r="C25" t="s">
         <v>47</v>
       </c>
@@ -2192,8 +2174,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="71"/>
-      <c r="B26" s="75"/>
+      <c r="A26" s="65"/>
+      <c r="B26" s="68"/>
       <c r="C26" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2190,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="71"/>
-      <c r="B27" s="75"/>
+      <c r="A27" s="65"/>
+      <c r="B27" s="68"/>
       <c r="C27" t="s">
         <v>17</v>
       </c>
@@ -2224,8 +2206,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="71"/>
-      <c r="B28" s="75"/>
+      <c r="A28" s="65"/>
+      <c r="B28" s="68"/>
       <c r="C28" t="s">
         <v>114</v>
       </c>
@@ -2240,8 +2222,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="71"/>
-      <c r="B29" s="76" t="s">
+      <c r="A29" s="65"/>
+      <c r="B29" s="69" t="s">
         <v>256</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -2258,137 +2240,137 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="71"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="48" t="s">
+      <c r="A30" s="65"/>
+      <c r="B30" s="72"/>
+      <c r="C30" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" t="s">
         <v>67</v>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="13">
         <f>E31*4</f>
         <v>424</v>
       </c>
-      <c r="F30" s="48" t="s">
+      <c r="F30" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="71"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="48" t="s">
+      <c r="A31" s="65"/>
+      <c r="B31" s="72"/>
+      <c r="C31" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="13">
         <v>106</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="F31" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="71"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="48" t="s">
+      <c r="A32" s="65"/>
+      <c r="B32" s="72"/>
+      <c r="C32" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="48" t="s">
+      <c r="D32" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="7">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="71"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="48" t="s">
+      <c r="A33" s="65"/>
+      <c r="B33" s="72"/>
+      <c r="C33" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="7">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F33" s="48" t="s">
+      <c r="F33" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="71"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="48" t="s">
+      <c r="A34" s="65"/>
+      <c r="B34" s="72"/>
+      <c r="C34" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="48" t="s">
+      <c r="D34" t="s">
         <v>72</v>
       </c>
-      <c r="E34" s="50">
+      <c r="E34" s="7">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F34" s="48" t="s">
+      <c r="F34" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="71"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="48" t="s">
+      <c r="A35" s="65"/>
+      <c r="B35" s="72"/>
+      <c r="C35" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="49">
+      <c r="E35" s="13">
         <v>0.25</v>
       </c>
-      <c r="F35" s="48" t="s">
+      <c r="F35" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="71"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="48" t="s">
+      <c r="A36" s="65"/>
+      <c r="B36" s="72"/>
+      <c r="C36" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="48" t="s">
+      <c r="D36" t="s">
         <v>73</v>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="7">
         <v>0</v>
       </c>
-      <c r="F36" s="48" t="s">
+      <c r="F36" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="71"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="48" t="s">
+      <c r="A37" s="65"/>
+      <c r="B37" s="72"/>
+      <c r="C37" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="48" t="s">
+      <c r="D37" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="21">
         <v>15</v>
       </c>
-      <c r="F37" s="48" t="s">
+      <c r="F37" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="72"/>
-      <c r="B38" s="80"/>
+      <c r="A38" s="66"/>
+      <c r="B38" s="73"/>
       <c r="C38" s="14" t="s">
         <v>17</v>
       </c>
@@ -2403,64 +2385,64 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="55" t="s">
+      <c r="D39" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="56">
+      <c r="E39" s="50">
         <v>0.1699</v>
       </c>
-      <c r="F39" s="55" t="s">
+      <c r="F39" s="49" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="73"/>
-      <c r="B40" s="64" t="s">
+      <c r="A40" s="65"/>
+      <c r="B40" s="58" t="s">
         <v>300</v>
       </c>
-      <c r="C40" s="65" t="s">
+      <c r="C40" s="59" t="s">
         <v>301</v>
       </c>
-      <c r="D40" s="65" t="s">
+      <c r="D40" s="59" t="s">
         <v>302</v>
       </c>
-      <c r="E40" s="66">
+      <c r="E40" s="60">
         <v>0.2</v>
       </c>
-      <c r="F40" s="65" t="s">
+      <c r="F40" s="59" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="73"/>
-      <c r="B41" s="57" t="s">
+      <c r="A41" s="65"/>
+      <c r="B41" s="51" t="s">
         <v>297</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="52" t="s">
         <v>298</v>
       </c>
-      <c r="D41" s="58" t="s">
+      <c r="D41" s="52" t="s">
         <v>299</v>
       </c>
-      <c r="E41" s="59">
+      <c r="E41" s="53">
         <v>5</v>
       </c>
-      <c r="F41" s="58" t="s">
+      <c r="F41" s="52" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="71"/>
-      <c r="B42" s="76" t="s">
+      <c r="A42" s="65"/>
+      <c r="B42" s="69" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2477,8 +2459,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="71"/>
-      <c r="B43" s="75"/>
+      <c r="A43" s="65"/>
+      <c r="B43" s="68"/>
       <c r="C43" t="s">
         <v>12</v>
       </c>
@@ -2493,8 +2475,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="71"/>
-      <c r="B44" s="75"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="68"/>
       <c r="C44" t="s">
         <v>19</v>
       </c>
@@ -2509,8 +2491,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="71"/>
-      <c r="B45" s="75"/>
+      <c r="A45" s="65"/>
+      <c r="B45" s="68"/>
       <c r="C45" t="s">
         <v>20</v>
       </c>
@@ -2525,8 +2507,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="71"/>
-      <c r="B46" s="75"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="68"/>
       <c r="C46" t="s">
         <v>15</v>
       </c>
@@ -2541,8 +2523,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="71"/>
-      <c r="B47" s="75"/>
+      <c r="A47" s="65"/>
+      <c r="B47" s="68"/>
       <c r="C47" t="s">
         <v>82</v>
       </c>
@@ -2557,8 +2539,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="71"/>
-      <c r="B48" s="77"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="70"/>
       <c r="C48" s="5" t="s">
         <v>17</v>
       </c>
@@ -2573,8 +2555,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="71"/>
-      <c r="B49" s="76" t="s">
+      <c r="A49" s="65"/>
+      <c r="B49" s="69" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -2591,8 +2573,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="71"/>
-      <c r="B50" s="75"/>
+      <c r="A50" s="65"/>
+      <c r="B50" s="68"/>
       <c r="C50" t="s">
         <v>12</v>
       </c>
@@ -2607,8 +2589,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="71"/>
-      <c r="B51" s="75"/>
+      <c r="A51" s="65"/>
+      <c r="B51" s="68"/>
       <c r="C51" t="s">
         <v>19</v>
       </c>
@@ -2623,8 +2605,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="71"/>
-      <c r="B52" s="75"/>
+      <c r="A52" s="65"/>
+      <c r="B52" s="68"/>
       <c r="C52" t="s">
         <v>20</v>
       </c>
@@ -2639,8 +2621,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="71"/>
-      <c r="B53" s="75"/>
+      <c r="A53" s="65"/>
+      <c r="B53" s="68"/>
       <c r="C53" t="s">
         <v>15</v>
       </c>
@@ -2655,8 +2637,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="71"/>
-      <c r="B54" s="75"/>
+      <c r="A54" s="65"/>
+      <c r="B54" s="68"/>
       <c r="C54" t="s">
         <v>82</v>
       </c>
@@ -2671,8 +2653,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="72"/>
-      <c r="B55" s="78"/>
+      <c r="A55" s="66"/>
+      <c r="B55" s="71"/>
       <c r="C55" s="14" t="s">
         <v>17</v>
       </c>
@@ -2687,7 +2669,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="70" t="s">
+      <c r="A56" s="64" t="s">
         <v>90</v>
       </c>
       <c r="B56" s="16" t="s">
@@ -2707,7 +2689,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="71"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="17" t="s">
         <v>93</v>
       </c>
@@ -2725,7 +2707,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="72"/>
+      <c r="A58" s="66"/>
       <c r="B58" s="1" t="s">
         <v>94</v>
       </c>
@@ -2797,10 +2779,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="87" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="27" t="s">
@@ -2815,8 +2797,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="94"/>
-      <c r="B3" s="98"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="88"/>
       <c r="C3" s="12" t="s">
         <v>135</v>
       </c>
@@ -2829,8 +2811,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="94"/>
-      <c r="B4" s="98"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="88"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
@@ -2843,8 +2825,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="94"/>
-      <c r="B5" s="98"/>
+      <c r="A5" s="85"/>
+      <c r="B5" s="88"/>
       <c r="C5" s="12" t="s">
         <v>171</v>
       </c>
@@ -2857,8 +2839,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="94"/>
-      <c r="B6" s="98"/>
+      <c r="A6" s="85"/>
+      <c r="B6" s="88"/>
       <c r="C6" s="12" t="s">
         <v>183</v>
       </c>
@@ -2871,8 +2853,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="94"/>
-      <c r="B7" s="98"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="12" t="s">
         <v>201</v>
       </c>
@@ -2885,8 +2867,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="94"/>
-      <c r="B8" s="98"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="88"/>
       <c r="C8" s="12" t="s">
         <v>249</v>
       </c>
@@ -2899,8 +2881,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="94"/>
-      <c r="B9" s="98"/>
+      <c r="A9" s="85"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="12" t="s">
         <v>215</v>
       </c>
@@ -2913,8 +2895,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="94"/>
-      <c r="B10" s="98"/>
+      <c r="A10" s="85"/>
+      <c r="B10" s="88"/>
       <c r="C10" s="12" t="s">
         <v>239</v>
       </c>
@@ -2927,13 +2909,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="94"/>
-      <c r="B11" s="98"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="88"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="94"/>
-      <c r="B12" s="100" t="s">
+      <c r="A12" s="85"/>
+      <c r="B12" s="90" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="36" t="s">
@@ -2948,8 +2930,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
-      <c r="B13" s="98"/>
+      <c r="A13" s="85"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="12" t="s">
         <v>176</v>
       </c>
@@ -2962,8 +2944,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="94"/>
-      <c r="B14" s="98"/>
+      <c r="A14" s="85"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="12" t="s">
         <v>179</v>
       </c>
@@ -2976,8 +2958,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="94"/>
-      <c r="B15" s="98"/>
+      <c r="A15" s="85"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="12" t="s">
         <v>180</v>
       </c>
@@ -2990,8 +2972,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="94"/>
-      <c r="B16" s="98"/>
+      <c r="A16" s="85"/>
+      <c r="B16" s="88"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
@@ -3004,8 +2986,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="94"/>
-      <c r="B17" s="98"/>
+      <c r="A17" s="85"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="12" t="s">
         <v>183</v>
       </c>
@@ -3018,8 +3000,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="94"/>
-      <c r="B18" s="98"/>
+      <c r="A18" s="85"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="12" t="s">
         <v>201</v>
       </c>
@@ -3032,8 +3014,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="94"/>
-      <c r="B19" s="98"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="88"/>
       <c r="C19" s="12" t="s">
         <v>249</v>
       </c>
@@ -3046,8 +3028,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="94"/>
-      <c r="B20" s="98"/>
+      <c r="A20" s="85"/>
+      <c r="B20" s="88"/>
       <c r="C20" s="12" t="s">
         <v>215</v>
       </c>
@@ -3060,8 +3042,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="94"/>
-      <c r="B21" s="98"/>
+      <c r="A21" s="85"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="12" t="s">
         <v>239</v>
       </c>
@@ -3074,16 +3056,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="94"/>
-      <c r="B22" s="99"/>
+      <c r="A22" s="85"/>
+      <c r="B22" s="89"/>
       <c r="C22" s="38"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39"/>
       <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="94"/>
-      <c r="B23" s="89" t="s">
+      <c r="A23" s="85"/>
+      <c r="B23" s="81" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -3098,8 +3080,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="94"/>
-      <c r="B24" s="89"/>
+      <c r="A24" s="85"/>
+      <c r="B24" s="81"/>
       <c r="C24" s="12" t="s">
         <v>135</v>
       </c>
@@ -3112,8 +3094,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="94"/>
-      <c r="B25" s="89"/>
+      <c r="A25" s="85"/>
+      <c r="B25" s="81"/>
       <c r="C25" s="12" t="s">
         <v>102</v>
       </c>
@@ -3126,8 +3108,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="94"/>
-      <c r="B26" s="89"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="81"/>
       <c r="C26" s="12" t="s">
         <v>173</v>
       </c>
@@ -3140,8 +3122,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="94"/>
-      <c r="B27" s="89"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="81"/>
       <c r="C27" s="12" t="s">
         <v>183</v>
       </c>
@@ -3154,8 +3136,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="94"/>
-      <c r="B28" s="89"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="81"/>
       <c r="C28" s="12" t="s">
         <v>201</v>
       </c>
@@ -3168,8 +3150,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="94"/>
-      <c r="B29" s="89"/>
+      <c r="A29" s="85"/>
+      <c r="B29" s="81"/>
       <c r="C29" s="12" t="s">
         <v>249</v>
       </c>
@@ -3182,8 +3164,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="94"/>
-      <c r="B30" s="89"/>
+      <c r="A30" s="85"/>
+      <c r="B30" s="81"/>
       <c r="C30" s="12" t="s">
         <v>215</v>
       </c>
@@ -3196,8 +3178,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="94"/>
-      <c r="B31" s="89"/>
+      <c r="A31" s="85"/>
+      <c r="B31" s="81"/>
       <c r="C31" s="12" t="s">
         <v>239</v>
       </c>
@@ -3210,15 +3192,15 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="94"/>
-      <c r="B32" s="89"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="81"/>
       <c r="E32" s="34"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="92" t="s">
+      <c r="A33" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="101" t="s">
+      <c r="B33" s="91" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="27" t="s">
@@ -3233,8 +3215,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="94"/>
-      <c r="B34" s="89"/>
+      <c r="A34" s="85"/>
+      <c r="B34" s="81"/>
       <c r="C34" s="12" t="s">
         <v>139</v>
       </c>
@@ -3247,8 +3229,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="94"/>
-      <c r="B35" s="89"/>
+      <c r="A35" s="85"/>
+      <c r="B35" s="81"/>
       <c r="C35" s="12" t="s">
         <v>168</v>
       </c>
@@ -3261,8 +3243,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="94"/>
-      <c r="B36" s="89"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="81"/>
       <c r="C36" s="12" t="s">
         <v>169</v>
       </c>
@@ -3275,8 +3257,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="94"/>
-      <c r="B37" s="89"/>
+      <c r="A37" s="85"/>
+      <c r="B37" s="81"/>
       <c r="C37" s="12" t="s">
         <v>183</v>
       </c>
@@ -3289,8 +3271,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="94"/>
-      <c r="B38" s="89"/>
+      <c r="A38" s="85"/>
+      <c r="B38" s="81"/>
       <c r="C38" s="12" t="s">
         <v>201</v>
       </c>
@@ -3303,8 +3285,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="94"/>
-      <c r="B39" s="89"/>
+      <c r="A39" s="85"/>
+      <c r="B39" s="81"/>
       <c r="C39" s="12" t="s">
         <v>249</v>
       </c>
@@ -3317,8 +3299,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="94"/>
-      <c r="B40" s="89"/>
+      <c r="A40" s="85"/>
+      <c r="B40" s="81"/>
       <c r="C40" s="12" t="s">
         <v>215</v>
       </c>
@@ -3331,8 +3313,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="94"/>
-      <c r="B41" s="89"/>
+      <c r="A41" s="85"/>
+      <c r="B41" s="81"/>
       <c r="C41" s="12" t="s">
         <v>239</v>
       </c>
@@ -3345,13 +3327,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="94"/>
-      <c r="B42" s="89"/>
+      <c r="A42" s="85"/>
+      <c r="B42" s="81"/>
       <c r="E42" s="34"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="94"/>
-      <c r="B43" s="88" t="s">
+      <c r="A43" s="85"/>
+      <c r="B43" s="80" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="36" t="s">
@@ -3366,8 +3348,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="94"/>
-      <c r="B44" s="89"/>
+      <c r="A44" s="85"/>
+      <c r="B44" s="81"/>
       <c r="C44" s="12" t="s">
         <v>141</v>
       </c>
@@ -3380,8 +3362,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="94"/>
-      <c r="B45" s="98"/>
+      <c r="A45" s="85"/>
+      <c r="B45" s="88"/>
       <c r="C45" s="12" t="s">
         <v>139</v>
       </c>
@@ -3394,8 +3376,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="94"/>
-      <c r="B46" s="98"/>
+      <c r="A46" s="85"/>
+      <c r="B46" s="88"/>
       <c r="C46" s="12" t="s">
         <v>135</v>
       </c>
@@ -3408,8 +3390,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="94"/>
-      <c r="B47" s="98"/>
+      <c r="A47" s="85"/>
+      <c r="B47" s="88"/>
       <c r="C47" s="12" t="s">
         <v>156</v>
       </c>
@@ -3422,8 +3404,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="94"/>
-      <c r="B48" s="98"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="88"/>
       <c r="C48" s="12" t="s">
         <v>157</v>
       </c>
@@ -3436,8 +3418,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="94"/>
-      <c r="B49" s="98"/>
+      <c r="A49" s="85"/>
+      <c r="B49" s="88"/>
       <c r="C49" s="12" t="s">
         <v>183</v>
       </c>
@@ -3450,8 +3432,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="94"/>
-      <c r="B50" s="98"/>
+      <c r="A50" s="85"/>
+      <c r="B50" s="88"/>
       <c r="C50" s="12" t="s">
         <v>201</v>
       </c>
@@ -3464,8 +3446,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="94"/>
-      <c r="B51" s="98"/>
+      <c r="A51" s="85"/>
+      <c r="B51" s="88"/>
       <c r="C51" s="12" t="s">
         <v>249</v>
       </c>
@@ -3478,8 +3460,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="94"/>
-      <c r="B52" s="98"/>
+      <c r="A52" s="85"/>
+      <c r="B52" s="88"/>
       <c r="C52" s="12" t="s">
         <v>215</v>
       </c>
@@ -3492,8 +3474,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="94"/>
-      <c r="B53" s="98"/>
+      <c r="A53" s="85"/>
+      <c r="B53" s="88"/>
       <c r="C53" s="12" t="s">
         <v>239</v>
       </c>
@@ -3506,18 +3488,18 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="95"/>
-      <c r="B54" s="102"/>
+      <c r="A54" s="86"/>
+      <c r="B54" s="92"/>
       <c r="C54" s="42"/>
       <c r="D54" s="42"/>
       <c r="E54" s="43"/>
       <c r="F54" s="42"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="92" t="s">
+      <c r="A55" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="96" t="s">
+      <c r="B55" s="87" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="27" t="s">
@@ -3532,8 +3514,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="94"/>
-      <c r="B56" s="98"/>
+      <c r="A56" s="85"/>
+      <c r="B56" s="88"/>
       <c r="C56" s="12" t="s">
         <v>199</v>
       </c>
@@ -3546,51 +3528,51 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="94"/>
-      <c r="B57" s="99"/>
+      <c r="A57" s="85"/>
+      <c r="B57" s="89"/>
       <c r="E57" s="32"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="94"/>
-      <c r="B58" s="85" t="s">
+      <c r="A58" s="85"/>
+      <c r="B58" s="77" t="s">
         <v>303</v>
       </c>
-      <c r="C58" s="60" t="s">
+      <c r="C58" s="54" t="s">
         <v>304</v>
       </c>
-      <c r="D58" s="60" t="s">
+      <c r="D58" s="54" t="s">
         <v>305</v>
       </c>
-      <c r="E58" s="61"/>
-      <c r="F58" s="60" t="s">
+      <c r="E58" s="55"/>
+      <c r="F58" s="54" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="94"/>
-      <c r="B59" s="86"/>
-      <c r="C59" s="62" t="s">
+      <c r="A59" s="85"/>
+      <c r="B59" s="78"/>
+      <c r="C59" s="56" t="s">
         <v>199</v>
       </c>
-      <c r="D59" s="62" t="s">
+      <c r="D59" s="56" t="s">
         <v>306</v>
       </c>
-      <c r="E59" s="63"/>
-      <c r="F59" s="62" t="s">
+      <c r="E59" s="57"/>
+      <c r="F59" s="56" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="94"/>
-      <c r="B60" s="87"/>
-      <c r="C60" s="62"/>
-      <c r="D60" s="62"/>
-      <c r="E60" s="63"/>
-      <c r="F60" s="62"/>
+      <c r="A60" s="85"/>
+      <c r="B60" s="79"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="56"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="94"/>
-      <c r="B61" s="88" t="s">
+      <c r="A61" s="85"/>
+      <c r="B61" s="80" t="s">
         <v>6</v>
       </c>
       <c r="C61" s="36" t="s">
@@ -3605,8 +3587,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="94"/>
-      <c r="B62" s="89"/>
+      <c r="A62" s="85"/>
+      <c r="B62" s="81"/>
       <c r="C62" s="12" t="s">
         <v>135</v>
       </c>
@@ -3619,8 +3601,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="94"/>
-      <c r="B63" s="89"/>
+      <c r="A63" s="85"/>
+      <c r="B63" s="81"/>
       <c r="C63" s="12" t="s">
         <v>151</v>
       </c>
@@ -3633,8 +3615,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="94"/>
-      <c r="B64" s="89"/>
+      <c r="A64" s="85"/>
+      <c r="B64" s="81"/>
       <c r="C64" s="12" t="s">
         <v>183</v>
       </c>
@@ -3647,8 +3629,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="94"/>
-      <c r="B65" s="89"/>
+      <c r="A65" s="85"/>
+      <c r="B65" s="81"/>
       <c r="C65" s="12" t="s">
         <v>201</v>
       </c>
@@ -3661,8 +3643,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="94"/>
-      <c r="B66" s="89"/>
+      <c r="A66" s="85"/>
+      <c r="B66" s="81"/>
       <c r="C66" s="12" t="s">
         <v>209</v>
       </c>
@@ -3675,8 +3657,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="94"/>
-      <c r="B67" s="89"/>
+      <c r="A67" s="85"/>
+      <c r="B67" s="81"/>
       <c r="C67" s="12" t="s">
         <v>249</v>
       </c>
@@ -3689,8 +3671,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="94"/>
-      <c r="B68" s="89"/>
+      <c r="A68" s="85"/>
+      <c r="B68" s="81"/>
       <c r="C68" s="12" t="s">
         <v>215</v>
       </c>
@@ -3703,8 +3685,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="94"/>
-      <c r="B69" s="89"/>
+      <c r="A69" s="85"/>
+      <c r="B69" s="81"/>
       <c r="C69" s="12" t="s">
         <v>239</v>
       </c>
@@ -3717,12 +3699,12 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="94"/>
-      <c r="B70" s="90"/>
+      <c r="A70" s="85"/>
+      <c r="B70" s="82"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="94"/>
-      <c r="B71" s="88" t="s">
+      <c r="A71" s="85"/>
+      <c r="B71" s="80" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="36" t="s">
@@ -3737,8 +3719,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="94"/>
-      <c r="B72" s="89"/>
+      <c r="A72" s="85"/>
+      <c r="B72" s="81"/>
       <c r="C72" s="12" t="s">
         <v>136</v>
       </c>
@@ -3751,8 +3733,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="94"/>
-      <c r="B73" s="89"/>
+      <c r="A73" s="85"/>
+      <c r="B73" s="81"/>
       <c r="C73" s="12" t="s">
         <v>149</v>
       </c>
@@ -3765,8 +3747,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="94"/>
-      <c r="B74" s="89"/>
+      <c r="A74" s="85"/>
+      <c r="B74" s="81"/>
       <c r="C74" s="12" t="s">
         <v>183</v>
       </c>
@@ -3779,8 +3761,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="94"/>
-      <c r="B75" s="89"/>
+      <c r="A75" s="85"/>
+      <c r="B75" s="81"/>
       <c r="C75" s="12" t="s">
         <v>201</v>
       </c>
@@ -3793,8 +3775,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="94"/>
-      <c r="B76" s="89"/>
+      <c r="A76" s="85"/>
+      <c r="B76" s="81"/>
       <c r="C76" s="12" t="s">
         <v>209</v>
       </c>
@@ -3807,8 +3789,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="94"/>
-      <c r="B77" s="89"/>
+      <c r="A77" s="85"/>
+      <c r="B77" s="81"/>
       <c r="C77" s="12" t="s">
         <v>249</v>
       </c>
@@ -3821,8 +3803,8 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="94"/>
-      <c r="B78" s="89"/>
+      <c r="A78" s="85"/>
+      <c r="B78" s="81"/>
       <c r="C78" s="12" t="s">
         <v>215</v>
       </c>
@@ -3835,8 +3817,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="94"/>
-      <c r="B79" s="89"/>
+      <c r="A79" s="85"/>
+      <c r="B79" s="81"/>
       <c r="C79" s="12" t="s">
         <v>239</v>
       </c>
@@ -3849,14 +3831,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
-      <c r="B80" s="91"/>
+      <c r="A80" s="86"/>
+      <c r="B80" s="83"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="92" t="s">
+      <c r="A81" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="96" t="s">
+      <c r="B81" s="87" t="s">
         <v>87</v>
       </c>
       <c r="C81" s="27" t="s">
@@ -3871,22 +3853,22 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="93"/>
-      <c r="B82" s="97"/>
-      <c r="C82" s="52" t="s">
+      <c r="A82" s="85"/>
+      <c r="B82" s="88"/>
+      <c r="C82" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="D82" s="52" t="s">
+      <c r="D82" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="E82" s="53"/>
-      <c r="F82" s="52" t="s">
+      <c r="E82" s="34"/>
+      <c r="F82" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="94"/>
-      <c r="B83" s="98"/>
+      <c r="A83" s="85"/>
+      <c r="B83" s="88"/>
       <c r="C83" s="12" t="s">
         <v>195</v>
       </c>
@@ -3899,13 +3881,13 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="94"/>
-      <c r="B84" s="99"/>
+      <c r="A84" s="85"/>
+      <c r="B84" s="89"/>
       <c r="E84" s="34"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="94"/>
-      <c r="B85" s="100" t="s">
+      <c r="A85" s="85"/>
+      <c r="B85" s="90" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="36" t="s">
@@ -3920,8 +3902,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="94"/>
-      <c r="B86" s="98"/>
+      <c r="A86" s="85"/>
+      <c r="B86" s="88"/>
       <c r="C86" s="12" t="s">
         <v>196</v>
       </c>
@@ -3934,16 +3916,16 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="94"/>
-      <c r="B87" s="99"/>
+      <c r="A87" s="85"/>
+      <c r="B87" s="89"/>
       <c r="C87" s="38"/>
       <c r="D87" s="38"/>
       <c r="E87" s="39"/>
       <c r="F87" s="38"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="94"/>
-      <c r="B88" s="100" t="s">
+      <c r="A88" s="85"/>
+      <c r="B88" s="90" t="s">
         <v>94</v>
       </c>
       <c r="C88" s="12" t="s">
@@ -3958,8 +3940,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="94"/>
-      <c r="B89" s="98"/>
+      <c r="A89" s="85"/>
+      <c r="B89" s="88"/>
       <c r="C89" s="12" t="s">
         <v>197</v>
       </c>
@@ -3972,18 +3954,18 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="95"/>
-      <c r="B90" s="102"/>
+      <c r="A90" s="86"/>
+      <c r="B90" s="92"/>
       <c r="C90" s="42"/>
       <c r="D90" s="42"/>
       <c r="E90" s="43"/>
       <c r="F90" s="42"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="92" t="s">
+      <c r="A91" s="84" t="s">
         <v>211</v>
       </c>
-      <c r="B91" s="96" t="s">
+      <c r="B91" s="87" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="27" t="s">
@@ -3998,8 +3980,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="93"/>
-      <c r="B92" s="98"/>
+      <c r="A92" s="85"/>
+      <c r="B92" s="88"/>
       <c r="C92" s="12" t="s">
         <v>224</v>
       </c>
@@ -4011,16 +3993,16 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="93"/>
-      <c r="B93" s="99"/>
+      <c r="A93" s="85"/>
+      <c r="B93" s="89"/>
       <c r="C93" s="38"/>
       <c r="D93" s="38"/>
       <c r="E93" s="38"/>
       <c r="F93" s="38"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="93"/>
-      <c r="B94" s="100" t="s">
+      <c r="A94" s="85"/>
+      <c r="B94" s="90" t="s">
         <v>234</v>
       </c>
       <c r="C94" s="12" t="s">
@@ -4034,8 +4016,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="93"/>
-      <c r="B95" s="98"/>
+      <c r="A95" s="85"/>
+      <c r="B95" s="88"/>
       <c r="C95" s="12" t="s">
         <v>232</v>
       </c>
@@ -4047,8 +4029,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="93"/>
-      <c r="B96" s="98"/>
+      <c r="A96" s="85"/>
+      <c r="B96" s="88"/>
       <c r="C96" s="12" t="s">
         <v>228</v>
       </c>
@@ -4060,8 +4042,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="93"/>
-      <c r="B97" s="98"/>
+      <c r="A97" s="85"/>
+      <c r="B97" s="88"/>
       <c r="C97" s="12" t="s">
         <v>230</v>
       </c>
@@ -4073,8 +4055,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="93"/>
-      <c r="B98" s="98"/>
+      <c r="A98" s="85"/>
+      <c r="B98" s="88"/>
       <c r="C98" s="12" t="s">
         <v>233</v>
       </c>
@@ -4086,8 +4068,8 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="93"/>
-      <c r="B99" s="98"/>
+      <c r="A99" s="85"/>
+      <c r="B99" s="88"/>
       <c r="C99" s="12" t="s">
         <v>242</v>
       </c>
@@ -4099,8 +4081,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="93"/>
-      <c r="B100" s="100" t="s">
+      <c r="A100" s="85"/>
+      <c r="B100" s="90" t="s">
         <v>263</v>
       </c>
       <c r="C100" s="36" t="s">
@@ -4115,120 +4097,112 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="93"/>
-      <c r="B101" s="97"/>
-      <c r="C101" s="52" t="s">
+      <c r="A101" s="85"/>
+      <c r="B101" s="88"/>
+      <c r="C101" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="D101" s="52" t="s">
+      <c r="D101" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="E101" s="52"/>
-      <c r="F101" s="52" t="s">
+      <c r="F101" s="12" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="93"/>
-      <c r="B102" s="97"/>
-      <c r="C102" s="52" t="s">
+      <c r="A102" s="85"/>
+      <c r="B102" s="88"/>
+      <c r="C102" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="D102" s="52" t="s">
+      <c r="D102" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="E102" s="52"/>
-      <c r="F102" s="52" t="s">
+      <c r="F102" s="12" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="93"/>
-      <c r="B103" s="97"/>
-      <c r="C103" s="52" t="s">
+      <c r="A103" s="85"/>
+      <c r="B103" s="88"/>
+      <c r="C103" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="D103" s="52" t="s">
+      <c r="D103" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="E103" s="52"/>
-      <c r="F103" s="52" t="s">
+      <c r="F103" s="12" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="93"/>
-      <c r="B104" s="97"/>
-      <c r="C104" s="52" t="s">
+      <c r="A104" s="85"/>
+      <c r="B104" s="88"/>
+      <c r="C104" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="D104" s="52" t="s">
+      <c r="D104" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52" t="s">
+      <c r="F104" s="12" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="93"/>
-      <c r="B105" s="97"/>
-      <c r="C105" s="52" t="s">
+      <c r="A105" s="85"/>
+      <c r="B105" s="88"/>
+      <c r="C105" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D105" s="52" t="s">
+      <c r="D105" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="E105" s="52"/>
-      <c r="F105" s="52" t="s">
+      <c r="F105" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="93"/>
-      <c r="B106" s="97"/>
-      <c r="C106" s="52" t="s">
+      <c r="A106" s="85"/>
+      <c r="B106" s="88"/>
+      <c r="C106" s="12" t="s">
         <v>257</v>
       </c>
       <c r="D106" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52" t="s">
+      <c r="F106" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="93"/>
-      <c r="B107" s="97"/>
-      <c r="C107" s="52" t="s">
+      <c r="A107" s="85"/>
+      <c r="B107" s="88"/>
+      <c r="C107" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="D107" s="52" t="s">
+      <c r="D107" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="E107" s="52"/>
       <c r="F107" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="93"/>
-      <c r="B108" s="97"/>
-      <c r="C108" s="52" t="s">
+      <c r="A108" s="85"/>
+      <c r="B108" s="88"/>
+      <c r="C108" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D108" s="52" t="s">
+      <c r="D108" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E108" s="52"/>
-      <c r="F108" s="52" t="s">
+      <c r="F108" s="12" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="93"/>
-      <c r="B109" s="100" t="s">
+      <c r="A109" s="85"/>
+      <c r="B109" s="90" t="s">
         <v>281</v>
       </c>
       <c r="C109" s="36" t="s">
@@ -4243,36 +4217,34 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="93"/>
-      <c r="B110" s="97"/>
-      <c r="C110" s="52" t="s">
+      <c r="A110" s="85"/>
+      <c r="B110" s="88"/>
+      <c r="C110" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="D110" s="52" t="s">
+      <c r="D110" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="E110" s="52"/>
-      <c r="F110" s="52" t="s">
+      <c r="F110" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="93"/>
-      <c r="B111" s="97"/>
-      <c r="C111" s="52" t="s">
+      <c r="A111" s="85"/>
+      <c r="B111" s="88"/>
+      <c r="C111" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="D111" s="52" t="s">
+      <c r="D111" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="E111" s="52"/>
-      <c r="F111" s="52" t="s">
+      <c r="F111" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="93"/>
-      <c r="B112" s="97"/>
+      <c r="A112" s="85"/>
+      <c r="B112" s="88"/>
       <c r="C112" s="12" t="s">
         <v>287</v>
       </c>
@@ -4284,12 +4256,12 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="93"/>
-      <c r="B113" s="99"/>
+      <c r="A113" s="85"/>
+      <c r="B113" s="89"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="93"/>
-      <c r="B114" s="100" t="s">
+      <c r="A114" s="85"/>
+      <c r="B114" s="90" t="s">
         <v>292</v>
       </c>
       <c r="C114" s="36" t="s">
@@ -4304,8 +4276,8 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="93"/>
-      <c r="B115" s="98"/>
+      <c r="A115" s="85"/>
+      <c r="B115" s="88"/>
       <c r="C115" s="12" t="s">
         <v>295</v>
       </c>
@@ -4317,7 +4289,7 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="93"/>
+      <c r="A116" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="22">

--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_HB_Höchst/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_HB_Höchst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_HB_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8FB2CC-2B7F-49F5-B49F-31140357E784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC967DA-5BF3-4821-A04B-4724A425B246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-53868" yWindow="3444" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="308">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1016,12 +1016,6 @@
   </si>
   <si>
     <t>calc_cost_nh3</t>
-  </si>
-  <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
   </si>
   <si>
     <t>Verkaufspreiseanalyse</t>
@@ -1083,10 +1077,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1254,29 +1248,29 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1289,36 +1283,36 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1327,9 +1321,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1370,6 +1364,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1379,44 +1406,11 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1821,7 +1815,7 @@
         <v>28</v>
       </c>
       <c r="E4" s="20">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="F4" t="s">
         <v>101</v>
@@ -1939,7 +1933,7 @@
         <v>453.5</v>
       </c>
       <c r="F11" s="63" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2407,13 +2401,13 @@
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="65"/>
       <c r="B40" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="C40" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="D40" s="59" t="s">
         <v>300</v>
-      </c>
-      <c r="C40" s="59" t="s">
-        <v>301</v>
-      </c>
-      <c r="D40" s="59" t="s">
-        <v>302</v>
       </c>
       <c r="E40" s="60">
         <v>0.2</v>
@@ -2425,13 +2419,13 @@
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="65"/>
       <c r="B41" s="51" t="s">
+        <v>295</v>
+      </c>
+      <c r="C41" s="52" t="s">
+        <v>296</v>
+      </c>
+      <c r="D41" s="52" t="s">
         <v>297</v>
-      </c>
-      <c r="C41" s="52" t="s">
-        <v>298</v>
-      </c>
-      <c r="D41" s="52" t="s">
-        <v>299</v>
       </c>
       <c r="E41" s="53">
         <v>5</v>
@@ -2682,7 +2676,7 @@
         <v>92</v>
       </c>
       <c r="E56" s="3">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>21</v>
@@ -2746,7 +2740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="12" customWidth="1"/>
@@ -2779,10 +2773,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="82" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="27" t="s">
@@ -2797,8 +2791,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="85"/>
-      <c r="B3" s="88"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="78"/>
       <c r="C3" s="12" t="s">
         <v>135</v>
       </c>
@@ -2811,8 +2805,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="85"/>
-      <c r="B4" s="88"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="78"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
@@ -2825,8 +2819,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="85"/>
-      <c r="B5" s="88"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="78"/>
       <c r="C5" s="12" t="s">
         <v>171</v>
       </c>
@@ -2839,8 +2833,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="85"/>
-      <c r="B6" s="88"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="78"/>
       <c r="C6" s="12" t="s">
         <v>183</v>
       </c>
@@ -2853,8 +2847,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="85"/>
-      <c r="B7" s="88"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="78"/>
       <c r="C7" s="12" t="s">
         <v>201</v>
       </c>
@@ -2867,8 +2861,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="85"/>
-      <c r="B8" s="88"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="78"/>
       <c r="C8" s="12" t="s">
         <v>249</v>
       </c>
@@ -2881,8 +2875,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="85"/>
-      <c r="B9" s="88"/>
+      <c r="A9" s="81"/>
+      <c r="B9" s="78"/>
       <c r="C9" s="12" t="s">
         <v>215</v>
       </c>
@@ -2895,8 +2889,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="85"/>
-      <c r="B10" s="88"/>
+      <c r="A10" s="81"/>
+      <c r="B10" s="78"/>
       <c r="C10" s="12" t="s">
         <v>239</v>
       </c>
@@ -2909,13 +2903,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="85"/>
-      <c r="B11" s="88"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="78"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="85"/>
-      <c r="B12" s="90" t="s">
+      <c r="A12" s="81"/>
+      <c r="B12" s="77" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="36" t="s">
@@ -2930,8 +2924,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
-      <c r="B13" s="88"/>
+      <c r="A13" s="81"/>
+      <c r="B13" s="78"/>
       <c r="C13" s="12" t="s">
         <v>176</v>
       </c>
@@ -2944,8 +2938,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="85"/>
-      <c r="B14" s="88"/>
+      <c r="A14" s="81"/>
+      <c r="B14" s="78"/>
       <c r="C14" s="12" t="s">
         <v>179</v>
       </c>
@@ -2958,8 +2952,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="85"/>
-      <c r="B15" s="88"/>
+      <c r="A15" s="81"/>
+      <c r="B15" s="78"/>
       <c r="C15" s="12" t="s">
         <v>180</v>
       </c>
@@ -2972,8 +2966,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="85"/>
-      <c r="B16" s="88"/>
+      <c r="A16" s="81"/>
+      <c r="B16" s="78"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
@@ -2986,8 +2980,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="85"/>
-      <c r="B17" s="88"/>
+      <c r="A17" s="81"/>
+      <c r="B17" s="78"/>
       <c r="C17" s="12" t="s">
         <v>183</v>
       </c>
@@ -3000,8 +2994,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="85"/>
-      <c r="B18" s="88"/>
+      <c r="A18" s="81"/>
+      <c r="B18" s="78"/>
       <c r="C18" s="12" t="s">
         <v>201</v>
       </c>
@@ -3014,8 +3008,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="85"/>
-      <c r="B19" s="88"/>
+      <c r="A19" s="81"/>
+      <c r="B19" s="78"/>
       <c r="C19" s="12" t="s">
         <v>249</v>
       </c>
@@ -3028,8 +3022,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="85"/>
-      <c r="B20" s="88"/>
+      <c r="A20" s="81"/>
+      <c r="B20" s="78"/>
       <c r="C20" s="12" t="s">
         <v>215</v>
       </c>
@@ -3042,8 +3036,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="85"/>
-      <c r="B21" s="88"/>
+      <c r="A21" s="81"/>
+      <c r="B21" s="78"/>
       <c r="C21" s="12" t="s">
         <v>239</v>
       </c>
@@ -3056,16 +3050,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="85"/>
-      <c r="B22" s="89"/>
+      <c r="A22" s="81"/>
+      <c r="B22" s="79"/>
       <c r="C22" s="38"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39"/>
       <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="85"/>
-      <c r="B23" s="81" t="s">
+      <c r="A23" s="81"/>
+      <c r="B23" s="83" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -3080,8 +3074,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="85"/>
-      <c r="B24" s="81"/>
+      <c r="A24" s="81"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="12" t="s">
         <v>135</v>
       </c>
@@ -3094,8 +3088,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
-      <c r="B25" s="81"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="12" t="s">
         <v>102</v>
       </c>
@@ -3108,8 +3102,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="85"/>
-      <c r="B26" s="81"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="83"/>
       <c r="C26" s="12" t="s">
         <v>173</v>
       </c>
@@ -3122,8 +3116,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="85"/>
-      <c r="B27" s="81"/>
+      <c r="A27" s="81"/>
+      <c r="B27" s="83"/>
       <c r="C27" s="12" t="s">
         <v>183</v>
       </c>
@@ -3136,8 +3130,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="85"/>
-      <c r="B28" s="81"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="83"/>
       <c r="C28" s="12" t="s">
         <v>201</v>
       </c>
@@ -3150,8 +3144,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="85"/>
-      <c r="B29" s="81"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="83"/>
       <c r="C29" s="12" t="s">
         <v>249</v>
       </c>
@@ -3164,8 +3158,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="85"/>
-      <c r="B30" s="81"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="83"/>
       <c r="C30" s="12" t="s">
         <v>215</v>
       </c>
@@ -3178,8 +3172,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="85"/>
-      <c r="B31" s="81"/>
+      <c r="A31" s="81"/>
+      <c r="B31" s="83"/>
       <c r="C31" s="12" t="s">
         <v>239</v>
       </c>
@@ -3192,15 +3186,15 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="85"/>
-      <c r="B32" s="81"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="83"/>
       <c r="E32" s="34"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="84" t="s">
+      <c r="A33" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="85" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="27" t="s">
@@ -3211,12 +3205,12 @@
       </c>
       <c r="E33" s="40"/>
       <c r="F33" s="27" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="85"/>
-      <c r="B34" s="81"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="83"/>
       <c r="C34" s="12" t="s">
         <v>139</v>
       </c>
@@ -3225,12 +3219,12 @@
       </c>
       <c r="E34" s="34"/>
       <c r="F34" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="85"/>
-      <c r="B35" s="81"/>
+      <c r="A35" s="81"/>
+      <c r="B35" s="83"/>
       <c r="C35" s="12" t="s">
         <v>168</v>
       </c>
@@ -3243,8 +3237,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="85"/>
-      <c r="B36" s="81"/>
+      <c r="A36" s="81"/>
+      <c r="B36" s="83"/>
       <c r="C36" s="12" t="s">
         <v>169</v>
       </c>
@@ -3257,8 +3251,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="85"/>
-      <c r="B37" s="81"/>
+      <c r="A37" s="81"/>
+      <c r="B37" s="83"/>
       <c r="C37" s="12" t="s">
         <v>183</v>
       </c>
@@ -3271,8 +3265,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="85"/>
-      <c r="B38" s="81"/>
+      <c r="A38" s="81"/>
+      <c r="B38" s="83"/>
       <c r="C38" s="12" t="s">
         <v>201</v>
       </c>
@@ -3285,8 +3279,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="85"/>
-      <c r="B39" s="81"/>
+      <c r="A39" s="81"/>
+      <c r="B39" s="83"/>
       <c r="C39" s="12" t="s">
         <v>249</v>
       </c>
@@ -3299,8 +3293,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="85"/>
-      <c r="B40" s="81"/>
+      <c r="A40" s="81"/>
+      <c r="B40" s="83"/>
       <c r="C40" s="12" t="s">
         <v>215</v>
       </c>
@@ -3313,8 +3307,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="85"/>
-      <c r="B41" s="81"/>
+      <c r="A41" s="81"/>
+      <c r="B41" s="83"/>
       <c r="C41" s="12" t="s">
         <v>239</v>
       </c>
@@ -3327,13 +3321,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="85"/>
-      <c r="B42" s="81"/>
+      <c r="A42" s="81"/>
+      <c r="B42" s="83"/>
       <c r="E42" s="34"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="85"/>
-      <c r="B43" s="80" t="s">
+      <c r="A43" s="81"/>
+      <c r="B43" s="86" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="36" t="s">
@@ -3348,8 +3342,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="85"/>
-      <c r="B44" s="81"/>
+      <c r="A44" s="81"/>
+      <c r="B44" s="83"/>
       <c r="C44" s="12" t="s">
         <v>141</v>
       </c>
@@ -3362,8 +3356,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="85"/>
-      <c r="B45" s="88"/>
+      <c r="A45" s="81"/>
+      <c r="B45" s="78"/>
       <c r="C45" s="12" t="s">
         <v>139</v>
       </c>
@@ -3376,8 +3370,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="85"/>
-      <c r="B46" s="88"/>
+      <c r="A46" s="81"/>
+      <c r="B46" s="78"/>
       <c r="C46" s="12" t="s">
         <v>135</v>
       </c>
@@ -3390,8 +3384,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="85"/>
-      <c r="B47" s="88"/>
+      <c r="A47" s="81"/>
+      <c r="B47" s="78"/>
       <c r="C47" s="12" t="s">
         <v>156</v>
       </c>
@@ -3404,8 +3398,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="85"/>
-      <c r="B48" s="88"/>
+      <c r="A48" s="81"/>
+      <c r="B48" s="78"/>
       <c r="C48" s="12" t="s">
         <v>157</v>
       </c>
@@ -3418,8 +3412,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="85"/>
-      <c r="B49" s="88"/>
+      <c r="A49" s="81"/>
+      <c r="B49" s="78"/>
       <c r="C49" s="12" t="s">
         <v>183</v>
       </c>
@@ -3432,8 +3426,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="85"/>
-      <c r="B50" s="88"/>
+      <c r="A50" s="81"/>
+      <c r="B50" s="78"/>
       <c r="C50" s="12" t="s">
         <v>201</v>
       </c>
@@ -3446,8 +3440,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="85"/>
-      <c r="B51" s="88"/>
+      <c r="A51" s="81"/>
+      <c r="B51" s="78"/>
       <c r="C51" s="12" t="s">
         <v>249</v>
       </c>
@@ -3460,8 +3454,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="85"/>
-      <c r="B52" s="88"/>
+      <c r="A52" s="81"/>
+      <c r="B52" s="78"/>
       <c r="C52" s="12" t="s">
         <v>215</v>
       </c>
@@ -3474,8 +3468,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="85"/>
-      <c r="B53" s="88"/>
+      <c r="A53" s="81"/>
+      <c r="B53" s="78"/>
       <c r="C53" s="12" t="s">
         <v>239</v>
       </c>
@@ -3488,18 +3482,18 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
-      <c r="B54" s="92"/>
+      <c r="A54" s="84"/>
+      <c r="B54" s="87"/>
       <c r="C54" s="42"/>
       <c r="D54" s="42"/>
       <c r="E54" s="43"/>
       <c r="F54" s="42"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="84" t="s">
+      <c r="A55" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="87" t="s">
+      <c r="B55" s="82" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="27" t="s">
@@ -3514,8 +3508,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="85"/>
-      <c r="B56" s="88"/>
+      <c r="A56" s="81"/>
+      <c r="B56" s="78"/>
       <c r="C56" s="12" t="s">
         <v>199</v>
       </c>
@@ -3528,20 +3522,20 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="85"/>
-      <c r="B57" s="89"/>
+      <c r="A57" s="81"/>
+      <c r="B57" s="79"/>
       <c r="E57" s="32"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="85"/>
-      <c r="B58" s="77" t="s">
+      <c r="A58" s="81"/>
+      <c r="B58" s="88" t="s">
+        <v>301</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>302</v>
+      </c>
+      <c r="D58" s="54" t="s">
         <v>303</v>
-      </c>
-      <c r="C58" s="54" t="s">
-        <v>304</v>
-      </c>
-      <c r="D58" s="54" t="s">
-        <v>305</v>
       </c>
       <c r="E58" s="55"/>
       <c r="F58" s="54" t="s">
@@ -3549,13 +3543,13 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="85"/>
-      <c r="B59" s="78"/>
+      <c r="A59" s="81"/>
+      <c r="B59" s="89"/>
       <c r="C59" s="56" t="s">
         <v>199</v>
       </c>
       <c r="D59" s="56" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E59" s="57"/>
       <c r="F59" s="56" t="s">
@@ -3563,16 +3557,16 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="85"/>
-      <c r="B60" s="79"/>
+      <c r="A60" s="81"/>
+      <c r="B60" s="90"/>
       <c r="C60" s="56"/>
       <c r="D60" s="56"/>
       <c r="E60" s="57"/>
       <c r="F60" s="56"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="85"/>
-      <c r="B61" s="80" t="s">
+      <c r="A61" s="81"/>
+      <c r="B61" s="86" t="s">
         <v>6</v>
       </c>
       <c r="C61" s="36" t="s">
@@ -3587,8 +3581,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="85"/>
-      <c r="B62" s="81"/>
+      <c r="A62" s="81"/>
+      <c r="B62" s="83"/>
       <c r="C62" s="12" t="s">
         <v>135</v>
       </c>
@@ -3601,8 +3595,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="85"/>
-      <c r="B63" s="81"/>
+      <c r="A63" s="81"/>
+      <c r="B63" s="83"/>
       <c r="C63" s="12" t="s">
         <v>151</v>
       </c>
@@ -3615,8 +3609,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="85"/>
-      <c r="B64" s="81"/>
+      <c r="A64" s="81"/>
+      <c r="B64" s="83"/>
       <c r="C64" s="12" t="s">
         <v>183</v>
       </c>
@@ -3629,8 +3623,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="85"/>
-      <c r="B65" s="81"/>
+      <c r="A65" s="81"/>
+      <c r="B65" s="83"/>
       <c r="C65" s="12" t="s">
         <v>201</v>
       </c>
@@ -3643,8 +3637,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="85"/>
-      <c r="B66" s="81"/>
+      <c r="A66" s="81"/>
+      <c r="B66" s="83"/>
       <c r="C66" s="12" t="s">
         <v>209</v>
       </c>
@@ -3657,8 +3651,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="85"/>
-      <c r="B67" s="81"/>
+      <c r="A67" s="81"/>
+      <c r="B67" s="83"/>
       <c r="C67" s="12" t="s">
         <v>249</v>
       </c>
@@ -3671,8 +3665,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="85"/>
-      <c r="B68" s="81"/>
+      <c r="A68" s="81"/>
+      <c r="B68" s="83"/>
       <c r="C68" s="12" t="s">
         <v>215</v>
       </c>
@@ -3685,8 +3679,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="85"/>
-      <c r="B69" s="81"/>
+      <c r="A69" s="81"/>
+      <c r="B69" s="83"/>
       <c r="C69" s="12" t="s">
         <v>239</v>
       </c>
@@ -3699,12 +3693,12 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="85"/>
-      <c r="B70" s="82"/>
+      <c r="A70" s="81"/>
+      <c r="B70" s="91"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="85"/>
-      <c r="B71" s="80" t="s">
+      <c r="A71" s="81"/>
+      <c r="B71" s="86" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="36" t="s">
@@ -3719,8 +3713,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="85"/>
-      <c r="B72" s="81"/>
+      <c r="A72" s="81"/>
+      <c r="B72" s="83"/>
       <c r="C72" s="12" t="s">
         <v>136</v>
       </c>
@@ -3733,8 +3727,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="85"/>
-      <c r="B73" s="81"/>
+      <c r="A73" s="81"/>
+      <c r="B73" s="83"/>
       <c r="C73" s="12" t="s">
         <v>149</v>
       </c>
@@ -3747,8 +3741,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="85"/>
-      <c r="B74" s="81"/>
+      <c r="A74" s="81"/>
+      <c r="B74" s="83"/>
       <c r="C74" s="12" t="s">
         <v>183</v>
       </c>
@@ -3761,8 +3755,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="85"/>
-      <c r="B75" s="81"/>
+      <c r="A75" s="81"/>
+      <c r="B75" s="83"/>
       <c r="C75" s="12" t="s">
         <v>201</v>
       </c>
@@ -3775,8 +3769,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="85"/>
-      <c r="B76" s="81"/>
+      <c r="A76" s="81"/>
+      <c r="B76" s="83"/>
       <c r="C76" s="12" t="s">
         <v>209</v>
       </c>
@@ -3789,8 +3783,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="85"/>
-      <c r="B77" s="81"/>
+      <c r="A77" s="81"/>
+      <c r="B77" s="83"/>
       <c r="C77" s="12" t="s">
         <v>249</v>
       </c>
@@ -3803,8 +3797,8 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="85"/>
-      <c r="B78" s="81"/>
+      <c r="A78" s="81"/>
+      <c r="B78" s="83"/>
       <c r="C78" s="12" t="s">
         <v>215</v>
       </c>
@@ -3817,8 +3811,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="85"/>
-      <c r="B79" s="81"/>
+      <c r="A79" s="81"/>
+      <c r="B79" s="83"/>
       <c r="C79" s="12" t="s">
         <v>239</v>
       </c>
@@ -3831,14 +3825,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
-      <c r="B80" s="83"/>
+      <c r="A80" s="84"/>
+      <c r="B80" s="92"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="84" t="s">
+      <c r="A81" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="87" t="s">
+      <c r="B81" s="82" t="s">
         <v>87</v>
       </c>
       <c r="C81" s="27" t="s">
@@ -3853,13 +3847,13 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="85"/>
-      <c r="B82" s="88"/>
+      <c r="A82" s="81"/>
+      <c r="B82" s="78"/>
       <c r="C82" s="12" t="s">
-        <v>291</v>
+        <v>195</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>290</v>
+        <v>191</v>
       </c>
       <c r="E82" s="34"/>
       <c r="F82" s="12" t="s">
@@ -3867,435 +3861,427 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="85"/>
-      <c r="B83" s="88"/>
-      <c r="C83" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>191</v>
-      </c>
+      <c r="A83" s="81"/>
+      <c r="B83" s="79"/>
       <c r="E83" s="34"/>
-      <c r="F83" s="12" t="s">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="81"/>
+      <c r="B84" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E84" s="41"/>
+      <c r="F84" s="36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="81"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E85" s="34"/>
+      <c r="F85" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="85"/>
-      <c r="B84" s="89"/>
-      <c r="E84" s="34"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="85"/>
-      <c r="B85" s="90" t="s">
-        <v>93</v>
-      </c>
-      <c r="C85" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="D85" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E85" s="41"/>
-      <c r="F85" s="36" t="s">
-        <v>163</v>
-      </c>
-    </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="85"/>
-      <c r="B86" s="88"/>
-      <c r="C86" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E86" s="34"/>
-      <c r="F86" s="12" t="s">
-        <v>194</v>
-      </c>
+      <c r="A86" s="81"/>
+      <c r="B86" s="79"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="38"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="85"/>
-      <c r="B87" s="89"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="38"/>
-      <c r="E87" s="39"/>
-      <c r="F87" s="38"/>
+      <c r="A87" s="81"/>
+      <c r="B87" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E87" s="34"/>
+      <c r="F87" s="12" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="85"/>
-      <c r="B88" s="90" t="s">
-        <v>94</v>
-      </c>
+      <c r="A88" s="81"/>
+      <c r="B88" s="78"/>
       <c r="C88" s="12" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E88" s="34"/>
       <c r="F88" s="12" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="85"/>
-      <c r="B89" s="88"/>
-      <c r="C89" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E89" s="34"/>
-      <c r="F89" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="86"/>
-      <c r="B90" s="92"/>
-      <c r="C90" s="42"/>
-      <c r="D90" s="42"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="42"/>
+    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="84"/>
+      <c r="B89" s="87"/>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="43"/>
+      <c r="F89" s="42"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="80" t="s">
+        <v>211</v>
+      </c>
+      <c r="B90" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D90" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="84" t="s">
-        <v>211</v>
-      </c>
-      <c r="B91" s="87" t="s">
-        <v>15</v>
-      </c>
-      <c r="C91" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="D91" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27" t="s">
+      <c r="A91" s="81"/>
+      <c r="B91" s="78"/>
+      <c r="C91" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F91" s="12" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="85"/>
-      <c r="B92" s="88"/>
-      <c r="C92" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F92" s="12" t="s">
-        <v>182</v>
-      </c>
+      <c r="A92" s="81"/>
+      <c r="B92" s="79"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="85"/>
-      <c r="B93" s="89"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38"/>
+      <c r="A93" s="81"/>
+      <c r="B93" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="85"/>
-      <c r="B94" s="90" t="s">
-        <v>234</v>
-      </c>
+      <c r="A94" s="81"/>
+      <c r="B94" s="78"/>
       <c r="C94" s="12" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F94" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="85"/>
-      <c r="B95" s="88"/>
+      <c r="A95" s="81"/>
+      <c r="B95" s="78"/>
       <c r="C95" s="12" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="85"/>
-      <c r="B96" s="88"/>
+      <c r="A96" s="81"/>
+      <c r="B96" s="78"/>
       <c r="C96" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F96" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="85"/>
-      <c r="B97" s="88"/>
+      <c r="A97" s="81"/>
+      <c r="B97" s="78"/>
       <c r="C97" s="12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F97" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="85"/>
-      <c r="B98" s="88"/>
+      <c r="A98" s="81"/>
+      <c r="B98" s="78"/>
       <c r="C98" s="12" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F98" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="85"/>
-      <c r="B99" s="88"/>
-      <c r="C99" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>194</v>
+      <c r="A99" s="81"/>
+      <c r="B99" s="77" t="s">
+        <v>263</v>
+      </c>
+      <c r="C99" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="D99" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="E99" s="36"/>
+      <c r="F99" s="36" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="85"/>
-      <c r="B100" s="90" t="s">
-        <v>263</v>
-      </c>
-      <c r="C100" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="D100" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36" t="s">
+      <c r="A100" s="81"/>
+      <c r="B100" s="78"/>
+      <c r="C100" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="F100" s="12" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="85"/>
-      <c r="B101" s="88"/>
+      <c r="A101" s="81"/>
+      <c r="B101" s="78"/>
       <c r="C101" s="12" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F101" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="81"/>
+      <c r="B102" s="78"/>
+      <c r="C102" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="F102" s="12" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="85"/>
-      <c r="B102" s="88"/>
-      <c r="C102" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="F102" s="12" t="s">
-        <v>278</v>
-      </c>
-    </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="85"/>
-      <c r="B103" s="88"/>
+      <c r="A103" s="81"/>
+      <c r="B103" s="78"/>
       <c r="C103" s="12" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="85"/>
-      <c r="B104" s="88"/>
+      <c r="A104" s="81"/>
+      <c r="B104" s="78"/>
       <c r="C104" s="12" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="85"/>
-      <c r="B105" s="88"/>
+      <c r="A105" s="81"/>
+      <c r="B105" s="78"/>
       <c r="C105" s="12" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F105" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="85"/>
-      <c r="B106" s="88"/>
+      <c r="A106" s="81"/>
+      <c r="B106" s="78"/>
       <c r="C106" s="12" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="F106" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="85"/>
-      <c r="B107" s="88"/>
+      <c r="A107" s="81"/>
+      <c r="B107" s="78"/>
       <c r="C107" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F107" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="81"/>
+      <c r="B108" s="77" t="s">
+        <v>281</v>
+      </c>
+      <c r="C108" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="D108" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="E108" s="36"/>
+      <c r="F108" s="36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="81"/>
+      <c r="B109" s="78"/>
+      <c r="C109" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="F109" s="12" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="85"/>
-      <c r="B108" s="88"/>
-      <c r="C108" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="F108" s="12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="85"/>
-      <c r="B109" s="90" t="s">
-        <v>281</v>
-      </c>
-      <c r="C109" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="D109" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="E109" s="36"/>
-      <c r="F109" s="36" t="s">
-        <v>265</v>
-      </c>
-    </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="85"/>
-      <c r="B110" s="88"/>
+      <c r="A110" s="81"/>
+      <c r="B110" s="78"/>
       <c r="C110" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F110" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="85"/>
-      <c r="B111" s="88"/>
+      <c r="A111" s="81"/>
+      <c r="B111" s="78"/>
       <c r="C111" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="85"/>
-      <c r="B112" s="88"/>
-      <c r="C112" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="F112" s="12" t="s">
-        <v>272</v>
-      </c>
+      <c r="A112" s="81"/>
+      <c r="B112" s="79"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="85"/>
-      <c r="B113" s="89"/>
+      <c r="A113" s="81"/>
+      <c r="B113" s="77" t="s">
+        <v>290</v>
+      </c>
+      <c r="C113" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="D113" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="85"/>
-      <c r="B114" s="90" t="s">
-        <v>292</v>
-      </c>
-      <c r="C114" s="36" t="s">
+      <c r="A114" s="81"/>
+      <c r="B114" s="78"/>
+      <c r="C114" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="D114" s="36" t="s">
+      <c r="D114" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="E114" s="36"/>
-      <c r="F114" s="36" t="s">
+      <c r="F114" s="12" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="85"/>
-      <c r="B115" s="88"/>
-      <c r="C115" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="85"/>
+      <c r="A115" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="B109:B113"/>
-    <mergeCell ref="A91:A116"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="A81:A89"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="A90:A115"/>
     <mergeCell ref="A2:A32"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -4303,18 +4289,12 @@
     <mergeCell ref="A33:A54"/>
     <mergeCell ref="B33:B42"/>
     <mergeCell ref="B43:B54"/>
-    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="B87:B89"/>
     <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B94:B99"/>
-    <mergeCell ref="B100:B108"/>
-    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="B99:B107"/>
+    <mergeCell ref="B90:B92"/>
     <mergeCell ref="A55:A80"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="B71:B80"/>
-    <mergeCell ref="A81:A90"/>
-    <mergeCell ref="B81:B84"/>
-    <mergeCell ref="B85:B87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
